--- a/important_mails_2026-09-16.xlsx
+++ b/important_mails_2026-09-16.xlsx
@@ -427,7 +427,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H276"/>
+  <dimension ref="A1:H275"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -533,7 +533,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>付款/资金类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -548,21 +548,67 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 07:08:09 +0000</t>
+          <t>Wed, 16 Sep 2026 12:07:50 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
+          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
+          <t>Strategies built for sellers at your stage—plus $200 off</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrvp/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
+[Secure your spot](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrvs/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
+Grow at any size
+This is the final week to register for Amazon Accelerate 2026! From September 22 to 24 in Seattle, get access to sessions, networking, and 1:1 expert access designed to meet you where you are.
+For a limited time, use code FLASH200 at checkout to save $200 and register for just $399. This offer won't last, so don't wait.
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrvs/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
+There's still time to register and experience:
+- New leadership on the mainstage
+Amit Agarwal, SVP of Worldwide Selling Partner Services &amp; International Emerging Markets, makes his Accelerate debut alongside Mary Beth Westmoreland, VP of Worldwide Selling Partner Experience, for a day one fireside chat. They'll cover how AI is already working on sellers' behalf, why the cost of selling is coming down, an</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>today</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 07:08:09 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -589,39 +635,39 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
+      <c r="B5" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:36:30 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -644,39 +690,39 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
+      <c r="B6" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:32:49 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Status materiałów niebezpiecznych (hazmat)
@@ -699,39 +745,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
+      <c r="B7" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:02:50 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -754,39 +800,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
+      <c r="B8" s="2" t="inlineStr">
         <is>
           <t>today</t>
         </is>
       </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:31:48 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>Dangerous goods (hazmat) status update</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>96
  Dangerous goods (hazmat) status update
@@ -809,39 +855,39 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B8" s="2" t="inlineStr">
+      <c r="B9" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -857,39 +903,39 @@
         </is>
       </c>
     </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B9" s="2" t="inlineStr">
+      <c r="B10" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
         <is>
           <t>Sun, 13 Sep 2026 04:42:34 +0000</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -905,39 +951,39 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B11" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:52:40 +0000</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -953,39 +999,39 @@
         </is>
       </c>
     </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B11" s="2" t="inlineStr">
+      <c r="B12" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:37:22 +0000</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1001,39 +1047,39 @@
         </is>
       </c>
     </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B12" s="2" t="inlineStr">
+      <c r="B13" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 05:39:06 +0000</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1049,39 +1095,39 @@
         </is>
       </c>
     </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B13" s="2" t="inlineStr">
+      <c r="B14" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 09:08:38 +0000</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1097,39 +1143,39 @@
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B14" s="2" t="inlineStr">
+      <c r="B15" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 05:04:40 +0000</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -1142,58 +1188,6 @@
 - In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
 - To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
 -</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 9 Sep 2026 11:29:22 +0000</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>Your FBA request is complete (YHD3zckrc9)</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>Greetings from Amazon.com
-We thought you'd like to know that we have completed your destroy request.
-You can track the status of this request by visiting your Seller Account at:
-https://sellercentral-europe.amazon.com/
-For a complete list of inventory being destroyed, go to:
-https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-3468543-8575644
-Please note: this email was sent from a notification-only address that
-cannot accept incoming e-mail. Please do not reply to this message.
-Thank you for using Fulfillment by Amazon.
-------------------------------------------------------------------------------
-Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
-and EU wide.
-------------------------------------------------------------------------------
-Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
-SPC-EUAmazon-175923552124772</t>
         </is>
       </c>
     </row>
@@ -1601,7 +1595,7 @@
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>产品链接/合规类</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
@@ -1616,126 +1610,22 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Wed, 9 Sep 2026 14:22:12 +0000</t>
+          <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>Rettifica del saldo negativo nei tuoi account</t>
+          <t>Submit proof of insurance by January 18 to avoid listing
+ deactivation</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr"/>
       <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Abbiamo rettificato il tuo saldo negativo di 149.05 € dovuto dal tuo account venditore Amazon.it in data settembre 9, 2026, utilizzando i fondi disponibili nel tuo account Amazon.fr. Puoi visualizzare il saldo del tuo account in qualsiasi momento accedendo al tuo account e quindi alla dashboard dei pagamenti .
-Per maggiori informazioni, vai a Rettifica del saldo negativo nei tuoi account .
-Distinti saluti,
-Amazon Payments Europe
- Segnala un problema con questa e-mail
- Per qualsiasi domanda consulta: Seller Central
- Per modificare le preferenze sulle e-mail consulta: Preferenze sulle notifiche
- Copyright 2026 Amazon, Inc. o società affiliate. Tutti i diritti riservati.
- Amazon Payments Europe
- 38 avenue John F. Kennedy,
- L-1855 Lussemburgo,
- Numero di registrazione in Lussemburgo: B-101818,
- Capitale Sociale 165.833 EUR,
- Numero di licenza di attività commerciale: 134248,
- Partita IVA n. LU 20260743.
- Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
- SPC-EUAmazon-738873504346435</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 9 Sep 2026 13:24:25 +0000</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>New sessions on AI, brand building, and account health</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4fj/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
-[Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
-New sessions. Built for where you are right now.
-The Amazon Accelerate 2026 agenda keeps getting better. We've added new sessions and experiences we think you’ll love.
-[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
-“Being in the room where it happened. Nothing replaces the energy of a live room full of real people... was an awesome experience. I learned new ways to connect with our consumers while growing profitably on Amazon. There's no other retailer that listens better to small business sellers, owners and brands than Amazon.”
-2025 attendee
-Here's what's new on the agenda:
-- AI tools you can use today
-New sessions on how to use AI-powered tools for listing creation, A+ Content optimization, and inventory planning—with step-by-step guidance you can apply immediately.
-- Brand</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B26" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D26" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>Submit proof of insurance by January 18 to avoid listing
- deactivation</t>
-        </is>
-      </c>
-      <c r="G26" s="2" t="inlineStr"/>
-      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
@@ -1751,40 +1641,40 @@
         </is>
       </c>
     </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B27" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 05:40:35 +0000</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -1803,39 +1693,39 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B28" s="2" t="inlineStr">
+      <c r="B26" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 15:50:06 +0000</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Submit product compliance documents to avoid listing removal</t>
         </is>
       </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
+      <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product compliance documents to avoid listing removal
@@ -1857,39 +1747,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 18:07:39 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -1907,89 +1797,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 9 Sep 2026 15:09:01 +0000</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 19:03:56 +0000</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product safety documentation to reactivate listings
- Hello Weihai US,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B31" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 15 Sep 2026 19:03:56 +0000</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Recover between 60-80%* from returns</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  We handle the grading and reselling. You keep control of pricing and recover value.
@@ -2012,39 +1852,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:54:49 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>Parcel Tax for Austrian B2C orders</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>Parcel Tax for Austrian B2C orders
  96
@@ -2055,39 +1895,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 00:43:23 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -2102,39 +1942,39 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 14:08:42 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>通过 Q4 活动拓展您的业务 — 尽早提报，节省费用</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -2166,39 +2006,39 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:39:41 +0000</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"Comunicados de Amazon Seller Central (no responder)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>[Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon
@@ -2214,205 +2054,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B36" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>货件/库存类</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 9 Sep 2026 16:45:36 +0000</t>
-        </is>
-      </c>
-      <c r="E36" s="2" t="inlineStr">
-        <is>
-          <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
-        </is>
-      </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的 Crifeton 团队：
-我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
-变更内容：亚马逊的系统现在会自动识别在您开启 OPR 之前发出的货件，并将其从 OPR 扫描评估范围中排除。这意味着您不再需要等待所有未应用 Transparency 透明计划标签的库存全部到达亚马逊运营中心后，再开启 OPR。
-这对您意味着什么?
-  1.  准备就绪（从现在开始所有商品都将正确应用 Transparency 透明计划标签）即可开启 OPR，无需再等待在途未应用 Transparency 透明计划标签货件全部入仓后再开启。
-  2.  无需再人工追踪未应用 Transparency 透明计划标签货件的入仓时间。
-  3.  您的 OPR 绩效数据将更加准确，因为仅包含应用了 Transparency 透明计划标签的产品的扫描结果。
-  4.  更快、更顺畅地让您的产品获得 Transparency 透明计划保护。
-您需要做什么？ 您的操作流程无需任何更改。请在您确保未来发出的货件（包括此前已创建但尚未发出的货件）都会正确应用 Transparency 透明计划标签时，即可开启 OPR。
-若您需要帮助：请联系您的 Transparency 透明计划经理或客户管理团队协助。
-常见问题
-Q1: OPR 扫描有哪些变化？
-亚马逊推出了货件感知处理流程（Shipment-Aware Processing），这是一项自动化流程旨在让您的 OPR 开启变得更加简单。在过去您需要谨慎考虑开启 OPR 的时间，以避免（已在途的）未应用 Transparency 透明计划标签的库存在亚马逊运营中心扫描时失败，从而影响您的运营表现评估的结果。而现在我们的系统会自动追踪您的货件日期，只扫描在您开启 OPR 之后发出的货件。任何在开启之前已经在途的库存都不会被扫描。
-Q2: 我需要有哪些不同的操作？
-您的操作流程无需更改。如果您能确保未来发出的货件（包括此前已创建但尚未发出的货件）都会正确应用 Transparency 透明计划标签时，那么就可以开启 OPR。您不再需要等待所有未应用 Transparency 透明计划标签的库存全部被亚马逊运营中心接收后再开启 OPR，系统会自动处理这一切。
-Q3: 我现有的未应用 Transparency 透明计划标签的库存会导致扫码失败吗？
-不会。任何在您开启 OPR 之前发出的货件都会被扫描系统自动跳过。只有在您 OPR 开启日期之后发出的货件才会进行运营表现评估。
-Q4: 这会影响 OPR 通过（Graduation）的时间吗？
-不会。此项变更旨在优化您的 OPR 体验，消除 OPR 开启前库存因缺失 Trans</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B37" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 9 Sep 2026 16:45:33 +0000</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="inlineStr">
-        <is>
-          <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>尊敬的 Crifeton 团队：
-我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
-变更内容：亚马逊的系统现在会自动识别在您开启 OPR 之前发出的货件，并将其从 OPR 扫描评估范围中排除。这意味着您不再需要等待所有未应用 Transparency 透明计划标签的库存全部到达亚马逊运营中心后，再开启 OPR。
-这对您意味着什么?
-  1.  准备就绪（从现在开始所有商品都将正确应用 Transparency 透明计划标签）即可开启 OPR，无需再等待在途未应用 Transparency 透明计划标签货件全部入仓后再开启。
-  2.  无需再人工追踪未应用 Transparency 透明计划标签货件的入仓时间。
-  3.  您的 OPR 绩效数据将更加准确，因为仅包含应用了 Transparency 透明计划标签的产品的扫描结果。
-  4.  更快、更顺畅地让您的产品获得 Transparency 透明计划保护。
-您需要做什么？ 您的操作流程无需任何更改。请在您确保未来发出的货件（包括此前已创建但尚未发出的货件）都会正确应用 Transparency 透明计划标签时，即可开启 OPR。
-若您需要帮助：请联系您的 Transparency 透明计划经理或客户管理团队协助。
-常见问题
-Q1: OPR 扫描有哪些变化？
-亚马逊推出了货件感知处理流程（Shipment-Aware Processing），这是一项自动化流程旨在让您的 OPR 开启变得更加简单。在过去您需要谨慎考虑开启 OPR 的时间，以避免（已在途的）未应用 Transparency 透明计划标签的库存在亚马逊运营中心扫描时失败，从而影响您的运营表现评估的结果。而现在我们的系统会自动追踪您的货件日期，只扫描在您开启 OPR 之后发出的货件。任何在开启之前已经在途的库存都不会被扫描。
-Q2: 我需要有哪些不同的操作？
-您的操作流程无需更改。如果您能确保未来发出的货件（包括此前已创建但尚未发出的货件）都会正确应用 Transparency 透明计划标签时，那么就可以开启 OPR。您不再需要等待所有未应用 Transparency 透明计划标签的库存全部被亚马逊运营中心接收后再开启 OPR，系统会自动处理这一切。
-Q3: 我现有的未应用 Transparency 透明计划标签的库存会导致扫码失败吗？
-不会。任何在您开启 OPR 之前发出的货件都会被扫描系统自动跳过。只有在您 OPR 开启日期之后发出的货件才会进行运营表现评估。
-Q4: 这会影响 OPR 通过（Graduation）的时间吗？
-不会。此项变更旨在优化您的 OPR 体验，消除 OPR 开启前库存因缺失 Trans</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 9 Sep 2026 14:40:23 +0000</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026
- 96
-Hello,
-We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 8/2026 is now available in your Seller Central Account.
-To access your invoice, go to your Tax Document Library . In your Tax Document Library, you will be able to view, download or print your invoice.
-The Amazon Services Team
- Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
-Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 8/2026 est maintenant disponible dans votre compte Seller Central.
-Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
-Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
-Pour toute question, contactez le Support Vendeur.
-Cordialement,
-Amazon.ca
- Report an issue with this email
- If you have any questions visit: Seller Central
- To change your email preferences visit: Notification Preferences
- We hope you found this message to be useful. However, if you'd </t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:18:39 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-24</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2435,40 +2109,40 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
+      <c r="B34" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:43:34 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -2486,39 +2160,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 10:27:49 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -2546,39 +2220,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 14:01:06 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>Redesigned Seller Central becomes default 24 Sep</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
  Same powerful tools, built to grow with your business.
@@ -2593,40 +2267,40 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:24:54 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>[Amazon.fr] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.fr] One or More of Your Amazon Listings Have Been Search Suppressed
@@ -2643,39 +2317,91 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 9 Sep 2026 11:29:22 +0000</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Your FBA request is complete (YHD3zckrc9)</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>Greetings from Amazon.com
+We thought you'd like to know that we have completed your destroy request.
+You can track the status of this request by visiting your Seller Account at:
+https://sellercentral-europe.amazon.com/
+For a complete list of inventory being destroyed, go to:
+https://sellercentral-europe.amazon.com/gp/orders/fba-order-details.html?orderID=S02-3468543-8575644
+Please note: this email was sent from a notification-only address that
+cannot accept incoming e-mail. Please do not reply to this message.
+Thank you for using Fulfillment by Amazon.
+------------------------------------------------------------------------------
+Fulfilment by Amazon – let Amazon pick, pack and ship your orders domestically
+and EU wide.
+------------------------------------------------------------------------------
+Was this e-mail helpful? https://sellercentral.amazon.co.uk/gp/satisfaction/survey-form.html?ie=UTF8&amp;HMDName=NotificationBusEmailHMD&amp;customAttribute1Value=PRODUCT_REMOVAL_ORDER_SHIPPED_NOW
+SPC-EUAmazon-175923552124772</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:22:19 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2691,39 +2417,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 04:57:55 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2739,39 +2465,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 11:28:14 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (pWbU6lC/+G)</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2791,39 +2517,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:54:29 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2839,39 +2565,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 04:38:47 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2887,39 +2613,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 09:20:41 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2935,39 +2661,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 17:54:07 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4rjrNkqMZx)</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2987,39 +2713,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 05:00:38 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3035,39 +2761,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 10:49:16 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (j2jHyzbiUU)</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3087,39 +2813,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 04:50:31 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3135,39 +2861,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 19:31:35 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TrF4EN0N6o)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3192,39 +2918,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:06:42 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -3237,39 +2963,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 05:00:11 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3285,39 +3011,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sun, 30 Aug 2026 14:03:08 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3338,39 +3064,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 04:40:08 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3386,39 +3112,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 16:34:35 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0QNxXwzJgp)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3438,39 +3164,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 15:00:25 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -3484,39 +3210,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 09:22:31 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3532,39 +3258,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 04:53:03 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3580,39 +3306,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 05:02:47 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3628,39 +3354,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 23:58:41 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0Bix9UfQE5)</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3680,39 +3406,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 15:00:02 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -3723,39 +3449,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 04:58:09 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3771,39 +3497,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 18:49:27 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (qO7a7il03F)</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3823,39 +3549,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:33:42 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (aVWN9vWwFe)</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3875,39 +3601,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 05:00:58 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3923,39 +3649,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:55:04 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -3978,39 +3704,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:36:21 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Balance paid on your Amazon seller account
@@ -4028,39 +3754,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 04:55:13 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4076,39 +3802,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 03:28:54 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4124,39 +3850,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 16:10:20 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4177,39 +3903,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 15:24:40 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4230,39 +3956,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 04:58:18 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4278,39 +4004,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Wed, 19 Aug 2026 16:12:03 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4331,39 +4057,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 05:03:01 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4379,87 +4105,143 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 17 Aug 2026 04:53:18 +0000</t>
-        </is>
-      </c>
-      <c r="E79" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F79" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 9 Sep 2026 14:22:12 +0000</t>
+        </is>
+      </c>
+      <c r="E74" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F74" s="2" t="inlineStr">
+        <is>
+          <t>Rettifica del saldo negativo nei tuoi account</t>
+        </is>
+      </c>
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Abbiamo rettificato il tuo saldo negativo di 149.05 € dovuto dal tuo account venditore Amazon.it in data settembre 9, 2026, utilizzando i fondi disponibili nel tuo account Amazon.fr. Puoi visualizzare il saldo del tuo account in qualsiasi momento accedendo al tuo account e quindi alla dashboard dei pagamenti .
+Per maggiori informazioni, vai a Rettifica del saldo negativo nei tuoi account .
+Distinti saluti,
+Amazon Payments Europe
+ Segnala un problema con questa e-mail
+ Per qualsiasi domanda consulta: Seller Central
+ Per modificare le preferenze sulle e-mail consulta: Preferenze sulle notifiche
+ Copyright 2026 Amazon, Inc. o società affiliate. Tutti i diritti riservati.
+ Amazon Payments Europe
+ 38 avenue John F. Kennedy,
+ L-1855 Lussemburgo,
+ Numero di registrazione in Lussemburgo: B-101818,
+ Capitale Sociale 165.833 EUR,
+ Numero di licenza di attività commerciale: 134248,
+ Partita IVA n. LU 20260743.
+ Questa e-mail è stata inviata da un indirizzo e-mail non monitorato.
+ SPC-EUAmazon-738873504346435</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 9 Sep 2026 13:24:25 +0000</t>
+        </is>
+      </c>
+      <c r="E75" s="2" t="inlineStr">
+        <is>
+          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F75" s="2" t="inlineStr">
+        <is>
+          <t>New sessions on AI, brand building, and account health</t>
+        </is>
+      </c>
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4fj/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
+[Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
+New sessions. Built for where you are right now.
+The Amazon Accelerate 2026 agenda keeps getting better. We've added new sessions and experiences we think you’ll love.
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
+“Being in the room where it happened. Nothing replaces the energy of a live room full of real people... was an awesome experience. I learned new ways to connect with our consumers while growing profitably on Amazon. There's no other retailer that listens better to small business sellers, owners and brands than Amazon.”
+2025 attendee
+Here's what's new on the agenda:
+- AI tools you can use today
+New sessions on how to use AI-powered tools for listing creation, A+ Content optimization, and inventory planning—with step-by-step guidance you can apply immediately.
+- Brand</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 12:29:09 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Grow your Amazon business this September—$200 off registration</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmdj/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmdm/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
@@ -4474,39 +4256,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:43:26 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4526,39 +4308,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 14:14:20 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -4582,39 +4364,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 12:11:55 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>1:1 expert access, new AI tools, and $200 off—register now</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmcf/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmcj/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
@@ -4630,40 +4412,40 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 15:50:39 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>A note from Katie Scott: Your spot at Amazon Accelerate 2026 is
  waiting</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj9l/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj9p/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
@@ -4677,39 +4459,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 14:51:26 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4725,39 +4507,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:50:35 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4773,39 +4555,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:34:38 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Three weeks out. Have you registered?</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj8h/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj8l/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
@@ -4819,39 +4601,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:47:19 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4871,39 +4653,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:54 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4920,39 +4702,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4972,39 +4754,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:39:58 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Envía los números de registro de RAP antes del 30 de junio</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -5013,39 +4795,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 10:29:17 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends this Saturday—Register now</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-26/7z5f1dw/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5f1dz/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
@@ -5064,39 +4846,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:42:21 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5113,39 +4895,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:41:47 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5165,39 +4947,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 10:23:35 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Final Call: Early-bird pricing ends this Saturday, 8/29—Register now</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-25/7z5dp4h/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dp4l/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
@@ -5216,39 +4998,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 12:33:59 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>Sellers called this one of the highlights of Accelerate</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-24/7z5dhr3/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dhr6/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
@@ -5264,39 +5046,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:24:04 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5320,39 +5102,39 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 12:38:26 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends August 29. Save $100 now</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596lw/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596lz/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
@@ -5368,39 +5150,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:31 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5417,39 +5199,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:20 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5469,39 +5251,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends Saturday, Aug. 29—Save $100 before it's full price</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596mz/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596n3/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
@@ -5517,40 +5299,40 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 10:16:19 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>The fireside chat we teased is here. Early-bird pricing ends next
  week.</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bwt/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58bwx/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
@@ -5566,39 +5348,39 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:05:40 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5618,39 +5400,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:47 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5667,39 +5449,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:34 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5719,39 +5501,39 @@
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B106" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C106" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D106" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 12:23:03 +0000</t>
         </is>
       </c>
-      <c r="E106" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F106" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>You're exactly who Accelerate was designed for</t>
         </is>
       </c>
-      <c r="G106" s="2" t="inlineStr"/>
-      <c r="H106" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-18/7z58zcm/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
 [Your next level starts here](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58zcq/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
@@ -5766,40 +5548,40 @@
         </is>
       </c>
     </row>
-    <row r="107">
-      <c r="A107" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B107" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C107" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D107" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E107" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F107" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Live at Accelerate 2026: Mary Beth Westmoreland and Amit Agarwal
  fireside chat</t>
         </is>
       </c>
-      <c r="G107" s="2" t="inlineStr"/>
-      <c r="H107" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bxx/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58by1/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
@@ -5812,39 +5594,39 @@
         </is>
       </c>
     </row>
-    <row r="108">
-      <c r="A108" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B108" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C108" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D108" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:27:13 +0000</t>
         </is>
       </c>
-      <c r="E108" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F108" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G108" s="2" t="inlineStr"/>
-      <c r="H108" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5861,39 +5643,39 @@
         </is>
       </c>
     </row>
-    <row r="109">
-      <c r="A109" s="2" t="inlineStr">
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B109" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C109" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D109" s="2" t="inlineStr">
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:26:45 +0000</t>
         </is>
       </c>
-      <c r="E109" s="2" t="inlineStr">
+      <c r="E105" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F109" s="2" t="inlineStr">
+      <c r="F105" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G109" s="2" t="inlineStr"/>
-      <c r="H109" s="2" t="inlineStr">
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5913,39 +5695,89 @@
         </is>
       </c>
     </row>
-    <row r="110">
-      <c r="A110" s="2" t="inlineStr">
+    <row r="106">
+      <c r="A106" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B110" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C110" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D110" s="2" t="inlineStr">
+      <c r="B106" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C106" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D106" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 9 Sep 2026 15:09:01 +0000</t>
+        </is>
+      </c>
+      <c r="E106" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F106" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G106" s="2" t="inlineStr"/>
+      <c r="H106" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai US,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations, and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfill the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subjec</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B107" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C107" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D107" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 08:06:37 +0000</t>
         </is>
       </c>
-      <c r="E110" s="2" t="inlineStr">
+      <c r="E107" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F110" s="2" t="inlineStr">
+      <c r="F107" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G110" s="2" t="inlineStr"/>
-      <c r="H110" s="2" t="inlineStr">
+      <c r="G107" s="2" t="inlineStr"/>
+      <c r="H107" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -5963,39 +5795,39 @@
         </is>
       </c>
     </row>
-    <row r="111">
-      <c r="A111" s="2" t="inlineStr">
+    <row r="108">
+      <c r="A108" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B111" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C111" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D111" s="2" t="inlineStr">
+      <c r="B108" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C108" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D108" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 17:08:09 +0000</t>
         </is>
       </c>
-      <c r="E111" s="2" t="inlineStr">
+      <c r="E108" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F111" s="2" t="inlineStr">
+      <c r="F108" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G111" s="2" t="inlineStr"/>
-      <c r="H111" s="2" t="inlineStr">
+      <c r="G108" s="2" t="inlineStr"/>
+      <c r="H108" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6013,39 +5845,39 @@
         </is>
       </c>
     </row>
-    <row r="112">
-      <c r="A112" s="2" t="inlineStr">
+    <row r="109">
+      <c r="A109" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B112" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C112" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D112" s="2" t="inlineStr">
+      <c r="B109" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C109" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D109" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:07:40 +0000</t>
         </is>
       </c>
-      <c r="E112" s="2" t="inlineStr">
+      <c r="E109" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F112" s="2" t="inlineStr">
+      <c r="F109" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G112" s="2" t="inlineStr"/>
-      <c r="H112" s="2" t="inlineStr">
+      <c r="G109" s="2" t="inlineStr"/>
+      <c r="H109" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -6063,39 +5895,39 @@
         </is>
       </c>
     </row>
-    <row r="113">
-      <c r="A113" s="2" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B113" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C113" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D113" s="2" t="inlineStr">
+      <c r="B110" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C110" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D110" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 18:06:40 +0000</t>
         </is>
       </c>
-      <c r="E113" s="2" t="inlineStr">
+      <c r="E110" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F113" s="2" t="inlineStr">
+      <c r="F110" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G113" s="2" t="inlineStr"/>
-      <c r="H113" s="2" t="inlineStr">
+      <c r="G110" s="2" t="inlineStr"/>
+      <c r="H110" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6114,39 +5946,39 @@
         </is>
       </c>
     </row>
-    <row r="114">
-      <c r="A114" s="2" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B114" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C114" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D114" s="2" t="inlineStr">
+      <c r="B111" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C111" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D111" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:40:10 +0000</t>
         </is>
       </c>
-      <c r="E114" s="2" t="inlineStr">
+      <c r="E111" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F114" s="2" t="inlineStr">
+      <c r="F111" s="2" t="inlineStr">
         <is>
           <t>Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales</t>
         </is>
       </c>
-      <c r="G114" s="2" t="inlineStr"/>
-      <c r="H114" s="2" t="inlineStr">
+      <c r="G111" s="2" t="inlineStr"/>
+      <c r="H111" s="2" t="inlineStr">
         <is>
           <t>Votre facture pour les frais de paiement au titre de la REP pour les ventes sur Amazon.fr |
 Your VAT invoice for EPR Pay on Behalf charges for Amazon.fr sales
@@ -6159,39 +5991,39 @@
         </is>
       </c>
     </row>
-    <row r="115">
-      <c r="A115" s="2" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B115" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C115" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D115" s="2" t="inlineStr">
+      <c r="B112" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C112" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D112" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:27 +0000</t>
         </is>
       </c>
-      <c r="E115" s="2" t="inlineStr">
+      <c r="E112" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F115" s="2" t="inlineStr">
+      <c r="F112" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G115" s="2" t="inlineStr"/>
-      <c r="H115" s="2" t="inlineStr">
+      <c r="G112" s="2" t="inlineStr"/>
+      <c r="H112" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -6210,39 +6042,39 @@
         </is>
       </c>
     </row>
-    <row r="116">
-      <c r="A116" s="2" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B116" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C116" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D116" s="2" t="inlineStr">
+      <c r="B113" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C113" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D113" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 17:07:04 +0000</t>
         </is>
       </c>
-      <c r="E116" s="2" t="inlineStr">
+      <c r="E113" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F116" s="2" t="inlineStr">
+      <c r="F113" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G116" s="2" t="inlineStr"/>
-      <c r="H116" s="2" t="inlineStr">
+      <c r="G113" s="2" t="inlineStr"/>
+      <c r="H113" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6260,39 +6092,39 @@
         </is>
       </c>
     </row>
-    <row r="117">
-      <c r="A117" s="2" t="inlineStr">
+    <row r="114">
+      <c r="A114" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B117" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C117" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D117" s="2" t="inlineStr">
+      <c r="B114" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C114" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D114" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:08:31 +0000</t>
         </is>
       </c>
-      <c r="E117" s="2" t="inlineStr">
+      <c r="E114" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F117" s="2" t="inlineStr">
+      <c r="F114" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G117" s="2" t="inlineStr"/>
-      <c r="H117" s="2" t="inlineStr">
+      <c r="G114" s="2" t="inlineStr"/>
+      <c r="H114" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6309,39 +6141,39 @@
         </is>
       </c>
     </row>
-    <row r="118">
-      <c r="A118" s="2" t="inlineStr">
+    <row r="115">
+      <c r="A115" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B118" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C118" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D118" s="2" t="inlineStr">
+      <c r="B115" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C115" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D115" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:59:58 +0000</t>
         </is>
       </c>
-      <c r="E118" s="2" t="inlineStr">
+      <c r="E115" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F118" s="2" t="inlineStr">
+      <c r="F115" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G118" s="2" t="inlineStr"/>
-      <c r="H118" s="2" t="inlineStr">
+      <c r="G115" s="2" t="inlineStr"/>
+      <c r="H115" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6359,39 +6191,39 @@
         </is>
       </c>
     </row>
-    <row r="119">
-      <c r="A119" s="2" t="inlineStr">
+    <row r="116">
+      <c r="A116" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B119" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C119" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D119" s="2" t="inlineStr">
+      <c r="B116" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C116" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D116" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 20:39:32 +0000</t>
         </is>
       </c>
-      <c r="E119" s="2" t="inlineStr">
+      <c r="E116" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F119" s="2" t="inlineStr">
+      <c r="F116" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G119" s="2" t="inlineStr"/>
-      <c r="H119" s="2" t="inlineStr">
+      <c r="G116" s="2" t="inlineStr"/>
+      <c r="H116" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6409,39 +6241,39 @@
         </is>
       </c>
     </row>
-    <row r="120">
-      <c r="A120" s="2" t="inlineStr">
+    <row r="117">
+      <c r="A117" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B120" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C120" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D120" s="2" t="inlineStr">
+      <c r="B117" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C117" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D117" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 13:13:54 +0000</t>
         </is>
       </c>
-      <c r="E120" s="2" t="inlineStr">
+      <c r="E117" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F120" s="2" t="inlineStr">
+      <c r="F117" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G120" s="2" t="inlineStr"/>
-      <c r="H120" s="2" t="inlineStr">
+      <c r="G117" s="2" t="inlineStr"/>
+      <c r="H117" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6457,39 +6289,39 @@
         </is>
       </c>
     </row>
-    <row r="121">
-      <c r="A121" s="2" t="inlineStr">
+    <row r="118">
+      <c r="A118" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B121" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C121" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D121" s="2" t="inlineStr">
+      <c r="B118" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C118" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D118" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 20:46:54 +0000</t>
         </is>
       </c>
-      <c r="E121" s="2" t="inlineStr">
+      <c r="E118" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F121" s="2" t="inlineStr">
+      <c r="F118" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G121" s="2" t="inlineStr"/>
-      <c r="H121" s="2" t="inlineStr">
+      <c r="G118" s="2" t="inlineStr"/>
+      <c r="H118" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6507,39 +6339,39 @@
         </is>
       </c>
     </row>
-    <row r="122">
-      <c r="A122" s="2" t="inlineStr">
+    <row r="119">
+      <c r="A119" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B122" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C122" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D122" s="2" t="inlineStr">
+      <c r="B119" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C119" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D119" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 20:32:31 +0000</t>
         </is>
       </c>
-      <c r="E122" s="2" t="inlineStr">
+      <c r="E119" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F122" s="2" t="inlineStr">
+      <c r="F119" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G122" s="2" t="inlineStr"/>
-      <c r="H122" s="2" t="inlineStr">
+      <c r="G119" s="2" t="inlineStr"/>
+      <c r="H119" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6557,39 +6389,39 @@
         </is>
       </c>
     </row>
-    <row r="123">
-      <c r="A123" s="2" t="inlineStr">
+    <row r="120">
+      <c r="A120" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B123" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C123" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D123" s="2" t="inlineStr">
+      <c r="B120" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C120" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D120" s="2" t="inlineStr">
         <is>
           <t>Fri, 4 Sep 2026 13:10:03 +0000</t>
         </is>
       </c>
-      <c r="E123" s="2" t="inlineStr">
+      <c r="E120" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F123" s="2" t="inlineStr">
+      <c r="F120" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G123" s="2" t="inlineStr"/>
-      <c r="H123" s="2" t="inlineStr">
+      <c r="G120" s="2" t="inlineStr"/>
+      <c r="H120" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6606,39 +6438,39 @@
         </is>
       </c>
     </row>
-    <row r="124">
-      <c r="A124" s="2" t="inlineStr">
+    <row r="121">
+      <c r="A121" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B124" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C124" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D124" s="2" t="inlineStr">
+      <c r="B121" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C121" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D121" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:30:25 +0000</t>
         </is>
       </c>
-      <c r="E124" s="2" t="inlineStr">
+      <c r="E121" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F124" s="2" t="inlineStr">
+      <c r="F121" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G124" s="2" t="inlineStr"/>
-      <c r="H124" s="2" t="inlineStr">
+      <c r="G121" s="2" t="inlineStr"/>
+      <c r="H121" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6656,39 +6488,39 @@
         </is>
       </c>
     </row>
-    <row r="125">
-      <c r="A125" s="2" t="inlineStr">
+    <row r="122">
+      <c r="A122" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B125" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C125" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D125" s="2" t="inlineStr">
+      <c r="B122" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C122" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D122" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 20:14:40 +0000</t>
         </is>
       </c>
-      <c r="E125" s="2" t="inlineStr">
+      <c r="E122" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F125" s="2" t="inlineStr">
+      <c r="F122" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G125" s="2" t="inlineStr"/>
-      <c r="H125" s="2" t="inlineStr">
+      <c r="G122" s="2" t="inlineStr"/>
+      <c r="H122" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6706,39 +6538,39 @@
         </is>
       </c>
     </row>
-    <row r="126">
-      <c r="A126" s="2" t="inlineStr">
+    <row r="123">
+      <c r="A123" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B126" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C126" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D126" s="2" t="inlineStr">
+      <c r="B123" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C123" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D123" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 12:45:43 +0000</t>
         </is>
       </c>
-      <c r="E126" s="2" t="inlineStr">
+      <c r="E123" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F126" s="2" t="inlineStr">
+      <c r="F123" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G126" s="2" t="inlineStr"/>
-      <c r="H126" s="2" t="inlineStr">
+      <c r="G123" s="2" t="inlineStr"/>
+      <c r="H123" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -6754,39 +6586,39 @@
         </is>
       </c>
     </row>
-    <row r="127">
-      <c r="A127" s="2" t="inlineStr">
+    <row r="124">
+      <c r="A124" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B127" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C127" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D127" s="2" t="inlineStr">
+      <c r="B124" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C124" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D124" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 20:11:48 +0000</t>
         </is>
       </c>
-      <c r="E127" s="2" t="inlineStr">
+      <c r="E124" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F127" s="2" t="inlineStr">
+      <c r="F124" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G127" s="2" t="inlineStr"/>
-      <c r="H127" s="2" t="inlineStr">
+      <c r="G124" s="2" t="inlineStr"/>
+      <c r="H124" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6804,39 +6636,39 @@
         </is>
       </c>
     </row>
-    <row r="128">
-      <c r="A128" s="2" t="inlineStr">
+    <row r="125">
+      <c r="A125" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B128" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C128" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D128" s="2" t="inlineStr">
+      <c r="B125" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C125" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D125" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 19:56:44 +0000</t>
         </is>
       </c>
-      <c r="E128" s="2" t="inlineStr">
+      <c r="E125" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F128" s="2" t="inlineStr">
+      <c r="F125" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G128" s="2" t="inlineStr"/>
-      <c r="H128" s="2" t="inlineStr">
+      <c r="G125" s="2" t="inlineStr"/>
+      <c r="H125" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -6854,39 +6686,39 @@
         </is>
       </c>
     </row>
-    <row r="129">
-      <c r="A129" s="2" t="inlineStr">
+    <row r="126">
+      <c r="A126" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B129" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C129" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D129" s="2" t="inlineStr">
+      <c r="B126" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C126" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D126" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:41:56 +0000</t>
         </is>
       </c>
-      <c r="E129" s="2" t="inlineStr">
+      <c r="E126" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F129" s="2" t="inlineStr">
+      <c r="F126" s="2" t="inlineStr">
         <is>
           <t>Submit EPR registration numbers by June 30</t>
         </is>
       </c>
-      <c r="G129" s="2" t="inlineStr"/>
-      <c r="H129" s="2" t="inlineStr">
+      <c r="G126" s="2" t="inlineStr"/>
+      <c r="H126" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -6895,39 +6727,39 @@
         </is>
       </c>
     </row>
-    <row r="130">
-      <c r="A130" s="2" t="inlineStr">
+    <row r="127">
+      <c r="A127" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B130" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C130" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D130" s="2" t="inlineStr">
+      <c r="B127" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C127" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D127" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 16:03:11 +0800 (GMT+08:00)</t>
         </is>
       </c>
-      <c r="E130" s="2" t="inlineStr">
+      <c r="E127" s="2" t="inlineStr">
         <is>
           <t>苏浩然 &lt;suhr@cvc.org.cn&gt;</t>
         </is>
       </c>
-      <c r="F130" s="2" t="inlineStr">
+      <c r="F127" s="2" t="inlineStr">
         <is>
           <t>Amazon DV TIC</t>
         </is>
       </c>
-      <c r="G130" s="2" t="inlineStr"/>
-      <c r="H130" s="2" t="inlineStr">
+      <c r="G127" s="2" t="inlineStr"/>
+      <c r="H127" s="2" t="inlineStr">
         <is>
           <t>尊敬的卖家，您好。
 我们可以为您提供亚马逊DV验证报告服务。
@@ -6969,39 +6801,39 @@
         </is>
       </c>
     </row>
-    <row r="131">
-      <c r="A131" s="2" t="inlineStr">
+    <row r="128">
+      <c r="A128" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B131" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C131" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D131" s="2" t="inlineStr">
+      <c r="B128" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C128" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D128" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 03:08:21 +0000</t>
         </is>
       </c>
-      <c r="E131" s="2" t="inlineStr">
+      <c r="E128" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F131" s="2" t="inlineStr">
+      <c r="F128" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G131" s="2" t="inlineStr"/>
-      <c r="H131" s="2" t="inlineStr">
+      <c r="G128" s="2" t="inlineStr"/>
+      <c r="H128" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -7020,39 +6852,39 @@
         </is>
       </c>
     </row>
-    <row r="132">
-      <c r="A132" s="2" t="inlineStr">
+    <row r="129">
+      <c r="A129" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B132" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C132" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D132" s="2" t="inlineStr">
+      <c r="B129" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C129" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D129" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 15:47:49 +0000</t>
         </is>
       </c>
-      <c r="E132" s="2" t="inlineStr">
+      <c r="E129" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F132" s="2" t="inlineStr">
+      <c r="F129" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026</t>
         </is>
       </c>
-      <c r="G132" s="2" t="inlineStr"/>
-      <c r="H132" s="2" t="inlineStr">
+      <c r="G129" s="2" t="inlineStr"/>
+      <c r="H129" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026
  96
@@ -7062,39 +6894,39 @@
         </is>
       </c>
     </row>
-    <row r="133">
-      <c r="A133" s="2" t="inlineStr">
+    <row r="130">
+      <c r="A130" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B133" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C133" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D133" s="2" t="inlineStr">
+      <c r="B130" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C130" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D130" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:15:11 +0000</t>
         </is>
       </c>
-      <c r="E133" s="2" t="inlineStr">
+      <c r="E130" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F133" s="2" t="inlineStr">
+      <c r="F130" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G133" s="2" t="inlineStr"/>
-      <c r="H133" s="2" t="inlineStr">
+      <c r="G130" s="2" t="inlineStr"/>
+      <c r="H130" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7113,39 +6945,39 @@
         </is>
       </c>
     </row>
-    <row r="134">
-      <c r="A134" s="2" t="inlineStr">
+    <row r="131">
+      <c r="A131" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B134" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C134" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D134" s="2" t="inlineStr">
+      <c r="B131" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C131" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D131" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 08:11:05 +0000</t>
         </is>
       </c>
-      <c r="E134" s="2" t="inlineStr">
+      <c r="E131" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F134" s="2" t="inlineStr">
+      <c r="F131" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G134" s="2" t="inlineStr"/>
-      <c r="H134" s="2" t="inlineStr">
+      <c r="G131" s="2" t="inlineStr"/>
+      <c r="H131" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7164,39 +6996,39 @@
         </is>
       </c>
     </row>
-    <row r="135">
-      <c r="A135" s="2" t="inlineStr">
+    <row r="132">
+      <c r="A132" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B135" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C135" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D135" s="2" t="inlineStr">
+      <c r="B132" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C132" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D132" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 14:08:01 +0000</t>
         </is>
       </c>
-      <c r="E135" s="2" t="inlineStr">
+      <c r="E132" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F135" s="2" t="inlineStr">
+      <c r="F132" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G135" s="2" t="inlineStr"/>
-      <c r="H135" s="2" t="inlineStr">
+      <c r="G132" s="2" t="inlineStr"/>
+      <c r="H132" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -7214,39 +7046,39 @@
         </is>
       </c>
     </row>
-    <row r="136">
-      <c r="A136" s="2" t="inlineStr">
+    <row r="133">
+      <c r="A133" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B136" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C136" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D136" s="2" t="inlineStr">
+      <c r="B133" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C133" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D133" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:11:28 +0000</t>
         </is>
       </c>
-      <c r="E136" s="2" t="inlineStr">
+      <c r="E133" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F136" s="2" t="inlineStr">
+      <c r="F133" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G136" s="2" t="inlineStr"/>
-      <c r="H136" s="2" t="inlineStr">
+      <c r="G133" s="2" t="inlineStr"/>
+      <c r="H133" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7265,39 +7097,39 @@
         </is>
       </c>
     </row>
-    <row r="137">
-      <c r="A137" s="2" t="inlineStr">
+    <row r="134">
+      <c r="A134" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B137" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C137" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D137" s="2" t="inlineStr">
+      <c r="B134" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C134" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D134" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:08:21 +0000</t>
         </is>
       </c>
-      <c r="E137" s="2" t="inlineStr">
+      <c r="E134" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F137" s="2" t="inlineStr">
+      <c r="F134" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G137" s="2" t="inlineStr"/>
-      <c r="H137" s="2" t="inlineStr">
+      <c r="G134" s="2" t="inlineStr"/>
+      <c r="H134" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7316,39 +7148,39 @@
         </is>
       </c>
     </row>
-    <row r="138">
-      <c r="A138" s="2" t="inlineStr">
+    <row r="135">
+      <c r="A135" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B138" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C138" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D138" s="2" t="inlineStr">
+      <c r="B135" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C135" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D135" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:34 +0000</t>
         </is>
       </c>
-      <c r="E138" s="2" t="inlineStr">
+      <c r="E135" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F138" s="2" t="inlineStr">
+      <c r="F135" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G138" s="2" t="inlineStr"/>
-      <c r="H138" s="2" t="inlineStr">
+      <c r="G135" s="2" t="inlineStr"/>
+      <c r="H135" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7367,39 +7199,39 @@
         </is>
       </c>
     </row>
-    <row r="139">
-      <c r="A139" s="2" t="inlineStr">
+    <row r="136">
+      <c r="A136" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B139" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C139" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D139" s="2" t="inlineStr">
+      <c r="B136" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C136" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D136" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 08:07:29 +0000</t>
         </is>
       </c>
-      <c r="E139" s="2" t="inlineStr">
+      <c r="E136" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F139" s="2" t="inlineStr">
+      <c r="F136" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G139" s="2" t="inlineStr"/>
-      <c r="H139" s="2" t="inlineStr">
+      <c r="G136" s="2" t="inlineStr"/>
+      <c r="H136" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai EU,
@@ -7418,39 +7250,39 @@
         </is>
       </c>
     </row>
-    <row r="140">
-      <c r="A140" s="2" t="inlineStr">
+    <row r="137">
+      <c r="A137" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B140" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C140" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D140" s="2" t="inlineStr">
+      <c r="B137" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C137" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D137" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 14:07:29 +0000</t>
         </is>
       </c>
-      <c r="E140" s="2" t="inlineStr">
+      <c r="E137" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F140" s="2" t="inlineStr">
+      <c r="F137" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G140" s="2" t="inlineStr"/>
-      <c r="H140" s="2" t="inlineStr">
+      <c r="G137" s="2" t="inlineStr"/>
+      <c r="H137" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Submit product safety documentation to reactivate listings
@@ -7468,39 +7300,39 @@
         </is>
       </c>
     </row>
-    <row r="141">
-      <c r="A141" s="2" t="inlineStr">
+    <row r="138">
+      <c r="A138" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B141" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C141" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D141" s="2" t="inlineStr">
+      <c r="B138" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C138" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D138" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 13:07:04 +0000</t>
         </is>
       </c>
-      <c r="E141" s="2" t="inlineStr">
+      <c r="E138" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F141" s="2" t="inlineStr">
+      <c r="F138" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to avoid listing deactivation</t>
         </is>
       </c>
-      <c r="G141" s="2" t="inlineStr"/>
-      <c r="H141" s="2" t="inlineStr">
+      <c r="G138" s="2" t="inlineStr"/>
+      <c r="H138" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Hello Weihai CA,
@@ -7519,39 +7351,39 @@
         </is>
       </c>
     </row>
-    <row r="142">
-      <c r="A142" s="2" t="inlineStr">
+    <row r="139">
+      <c r="A139" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B142" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C142" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D142" s="2" t="inlineStr">
+      <c r="B139" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C139" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D139" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 09:06:58 +0000</t>
         </is>
       </c>
-      <c r="E142" s="2" t="inlineStr">
+      <c r="E139" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F142" s="2" t="inlineStr">
+      <c r="F139" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G142" s="2" t="inlineStr"/>
-      <c r="H142" s="2" t="inlineStr">
+      <c r="G139" s="2" t="inlineStr"/>
+      <c r="H139" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7569,39 +7401,39 @@
         </is>
       </c>
     </row>
-    <row r="143">
-      <c r="A143" s="2" t="inlineStr">
+    <row r="140">
+      <c r="A140" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B143" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C143" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D143" s="2" t="inlineStr">
+      <c r="B140" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C140" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D140" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 16:31:11 +0000</t>
         </is>
       </c>
-      <c r="E143" s="2" t="inlineStr">
+      <c r="E140" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Support &lt;merch.service05@amazon.co.uk&gt;</t>
         </is>
       </c>
-      <c r="F143" s="2" t="inlineStr">
+      <c r="F140" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 13205236962] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规</t>
         </is>
       </c>
-      <c r="G143" s="2" t="inlineStr"/>
-      <c r="H143" s="2" t="inlineStr">
+      <c r="G140" s="2" t="inlineStr"/>
+      <c r="H140" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 13205236962] 【需立即行动】请通过亚马逊认可的TIC服务商完成儿童玩具合规
@@ -7636,40 +7468,40 @@
         </is>
       </c>
     </row>
-    <row r="144">
-      <c r="A144" s="2" t="inlineStr">
+    <row r="141">
+      <c r="A141" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B144" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C144" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D144" s="2" t="inlineStr">
+      <c r="B141" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C141" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D141" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 06:47:57 +0000</t>
         </is>
       </c>
-      <c r="E144" s="2" t="inlineStr">
+      <c r="E141" s="2" t="inlineStr">
         <is>
           <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
         </is>
       </c>
-      <c r="F144" s="2" t="inlineStr">
+      <c r="F141" s="2" t="inlineStr">
         <is>
           <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
  A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
         </is>
       </c>
-      <c r="G144" s="2" t="inlineStr"/>
-      <c r="H144" s="2" t="inlineStr">
+      <c r="G141" s="2" t="inlineStr"/>
+      <c r="H141" s="2" t="inlineStr">
         <is>
           <t>96
 SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
@@ -7687,39 +7519,39 @@
         </is>
       </c>
     </row>
-    <row r="145">
-      <c r="A145" s="2" t="inlineStr">
+    <row r="142">
+      <c r="A142" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B145" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C145" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D145" s="2" t="inlineStr">
+      <c r="B142" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C142" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D142" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 16:08:02 +0000</t>
         </is>
       </c>
-      <c r="E145" s="2" t="inlineStr">
+      <c r="E142" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F145" s="2" t="inlineStr">
+      <c r="F142" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G145" s="2" t="inlineStr"/>
-      <c r="H145" s="2" t="inlineStr">
+      <c r="G142" s="2" t="inlineStr"/>
+      <c r="H142" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7737,39 +7569,39 @@
         </is>
       </c>
     </row>
-    <row r="146">
-      <c r="A146" s="2" t="inlineStr">
+    <row r="143">
+      <c r="A143" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B146" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C146" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D146" s="2" t="inlineStr">
+      <c r="B143" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C143" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D143" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 23:14:29 +0000</t>
         </is>
       </c>
-      <c r="E146" s="2" t="inlineStr">
+      <c r="E143" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F146" s="2" t="inlineStr">
+      <c r="F143" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G146" s="2" t="inlineStr"/>
-      <c r="H146" s="2" t="inlineStr">
+      <c r="G143" s="2" t="inlineStr"/>
+      <c r="H143" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7787,39 +7619,39 @@
         </is>
       </c>
     </row>
-    <row r="147">
-      <c r="A147" s="2" t="inlineStr">
+    <row r="144">
+      <c r="A144" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B147" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C147" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D147" s="2" t="inlineStr">
+      <c r="B144" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C144" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D144" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 12:34:53 +0000</t>
         </is>
       </c>
-      <c r="E147" s="2" t="inlineStr">
+      <c r="E144" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F147" s="2" t="inlineStr">
+      <c r="F144" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory - Action Required</t>
         </is>
       </c>
-      <c r="G147" s="2" t="inlineStr"/>
-      <c r="H147" s="2" t="inlineStr">
+      <c r="G144" s="2" t="inlineStr"/>
+      <c r="H144" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 You recently received a notice concerning the removal of your listing(s) for the product(s) below due to a safety recall.
@@ -7835,39 +7667,39 @@
         </is>
       </c>
     </row>
-    <row r="148">
-      <c r="A148" s="2" t="inlineStr">
+    <row r="145">
+      <c r="A145" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B148" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C148" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D148" s="2" t="inlineStr">
+      <c r="B145" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C145" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D145" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 23:11:47 +0000</t>
         </is>
       </c>
-      <c r="E148" s="2" t="inlineStr">
+      <c r="E145" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F148" s="2" t="inlineStr">
+      <c r="F145" s="2" t="inlineStr">
         <is>
           <t>Submit product safety documentation to reactivate listings</t>
         </is>
       </c>
-      <c r="G148" s="2" t="inlineStr"/>
-      <c r="H148" s="2" t="inlineStr">
+      <c r="G145" s="2" t="inlineStr"/>
+      <c r="H145" s="2" t="inlineStr">
         <is>
           <t>96
  Submit product safety documentation to reactivate listings
@@ -7885,39 +7717,39 @@
         </is>
       </c>
     </row>
-    <row r="149">
-      <c r="A149" s="2" t="inlineStr">
+    <row r="146">
+      <c r="A146" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B149" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C149" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D149" s="2" t="inlineStr">
+      <c r="B146" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C146" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D146" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 10:06:05 +0000</t>
         </is>
       </c>
-      <c r="E149" s="2" t="inlineStr">
+      <c r="E146" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F149" s="2" t="inlineStr">
+      <c r="F146" s="2" t="inlineStr">
         <is>
           <t>Submit missing VAT Registration Information</t>
         </is>
       </c>
-      <c r="G149" s="2" t="inlineStr"/>
-      <c r="H149" s="2" t="inlineStr">
+      <c r="G146" s="2" t="inlineStr"/>
+      <c r="H146" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">Amazon Services
  96
@@ -7941,6 +7773,172 @@
  We recommend that you contact your tax advisor to understand your obligations in each country that you sell in.
 Make sure you always keep your Tax Information up-to-date in Seller Central, for all the countries in which you have an obligation.
 For more information, visit European </t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B147" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C147" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D147" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 9 Sep 2026 16:45:36 +0000</t>
+        </is>
+      </c>
+      <c r="E147" s="2" t="inlineStr">
+        <is>
+          <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F147" s="2" t="inlineStr">
+        <is>
+          <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
+        </is>
+      </c>
+      <c r="G147" s="2" t="inlineStr"/>
+      <c r="H147" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的 Crifeton 团队：
+我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
+变更内容：亚马逊的系统现在会自动识别在您开启 OPR 之前发出的货件，并将其从 OPR 扫描评估范围中排除。这意味着您不再需要等待所有未应用 Transparency 透明计划标签的库存全部到达亚马逊运营中心后，再开启 OPR。
+这对您意味着什么?
+  1.  准备就绪（从现在开始所有商品都将正确应用 Transparency 透明计划标签）即可开启 OPR，无需再等待在途未应用 Transparency 透明计划标签货件全部入仓后再开启。
+  2.  无需再人工追踪未应用 Transparency 透明计划标签货件的入仓时间。
+  3.  您的 OPR 绩效数据将更加准确，因为仅包含应用了 Transparency 透明计划标签的产品的扫描结果。
+  4.  更快、更顺畅地让您的产品获得 Transparency 透明计划保护。
+您需要做什么？ 您的操作流程无需任何更改。请在您确保未来发出的货件（包括此前已创建但尚未发出的货件）都会正确应用 Transparency 透明计划标签时，即可开启 OPR。
+若您需要帮助：请联系您的 Transparency 透明计划经理或客户管理团队协助。
+常见问题
+Q1: OPR 扫描有哪些变化？
+亚马逊推出了货件感知处理流程（Shipment-Aware Processing），这是一项自动化流程旨在让您的 OPR 开启变得更加简单。在过去您需要谨慎考虑开启 OPR 的时间，以避免（已在途的）未应用 Transparency 透明计划标签的库存在亚马逊运营中心扫描时失败，从而影响您的运营表现评估的结果。而现在我们的系统会自动追踪您的货件日期，只扫描在您开启 OPR 之后发出的货件。任何在开启之前已经在途的库存都不会被扫描。
+Q2: 我需要有哪些不同的操作？
+您的操作流程无需更改。如果您能确保未来发出的货件（包括此前已创建但尚未发出的货件）都会正确应用 Transparency 透明计划标签时，那么就可以开启 OPR。您不再需要等待所有未应用 Transparency 透明计划标签的库存全部被亚马逊运营中心接收后再开启 OPR，系统会自动处理这一切。
+Q3: 我现有的未应用 Transparency 透明计划标签的库存会导致扫码失败吗？
+不会。任何在您开启 OPR 之前发出的货件都会被扫描系统自动跳过。只有在您 OPR 开启日期之后发出的货件才会进行运营表现评估。
+Q4: 这会影响 OPR 通过（Graduation）的时间吗？
+不会。此项变更旨在优化您的 OPR 体验，消除 OPR 开启前库存因缺失 Trans</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B148" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C148" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D148" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 9 Sep 2026 16:45:33 +0000</t>
+        </is>
+      </c>
+      <c r="E148" s="2" t="inlineStr">
+        <is>
+          <t>Transparency No Reply &lt;noreply-transparency@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F148" s="2" t="inlineStr">
+        <is>
+          <t>OPR 体验优化——无需再手动追踪货件  /  Improvement to Your OPR Experience — No More Manual Shipment Tracking</t>
+        </is>
+      </c>
+      <c r="G148" s="2" t="inlineStr"/>
+      <c r="H148" s="2" t="inlineStr">
+        <is>
+          <t>尊敬的 Crifeton 团队：
+我们很高兴地通知您，OPR（Operational Performance Review运营表现评估）流程迎来一项优化，这将使开启 OPR 变得更加简单，并且您无需再手动追踪货件。
+变更内容：亚马逊的系统现在会自动识别在您开启 OPR 之前发出的货件，并将其从 OPR 扫描评估范围中排除。这意味着您不再需要等待所有未应用 Transparency 透明计划标签的库存全部到达亚马逊运营中心后，再开启 OPR。
+这对您意味着什么?
+  1.  准备就绪（从现在开始所有商品都将正确应用 Transparency 透明计划标签）即可开启 OPR，无需再等待在途未应用 Transparency 透明计划标签货件全部入仓后再开启。
+  2.  无需再人工追踪未应用 Transparency 透明计划标签货件的入仓时间。
+  3.  您的 OPR 绩效数据将更加准确，因为仅包含应用了 Transparency 透明计划标签的产品的扫描结果。
+  4.  更快、更顺畅地让您的产品获得 Transparency 透明计划保护。
+您需要做什么？ 您的操作流程无需任何更改。请在您确保未来发出的货件（包括此前已创建但尚未发出的货件）都会正确应用 Transparency 透明计划标签时，即可开启 OPR。
+若您需要帮助：请联系您的 Transparency 透明计划经理或客户管理团队协助。
+常见问题
+Q1: OPR 扫描有哪些变化？
+亚马逊推出了货件感知处理流程（Shipment-Aware Processing），这是一项自动化流程旨在让您的 OPR 开启变得更加简单。在过去您需要谨慎考虑开启 OPR 的时间，以避免（已在途的）未应用 Transparency 透明计划标签的库存在亚马逊运营中心扫描时失败，从而影响您的运营表现评估的结果。而现在我们的系统会自动追踪您的货件日期，只扫描在您开启 OPR 之后发出的货件。任何在开启之前已经在途的库存都不会被扫描。
+Q2: 我需要有哪些不同的操作？
+您的操作流程无需更改。如果您能确保未来发出的货件（包括此前已创建但尚未发出的货件）都会正确应用 Transparency 透明计划标签时，那么就可以开启 OPR。您不再需要等待所有未应用 Transparency 透明计划标签的库存全部被亚马逊运营中心接收后再开启 OPR，系统会自动处理这一切。
+Q3: 我现有的未应用 Transparency 透明计划标签的库存会导致扫码失败吗？
+不会。任何在您开启 OPR 之前发出的货件都会被扫描系统自动跳过。只有在您 OPR 开启日期之后发出的货件才会进行运营表现评估。
+Q4: 这会影响 OPR 通过（Graduation）的时间吗？
+不会。此项变更旨在优化您的 OPR 体验，消除 OPR 开启前库存因缺失 Trans</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="2" t="inlineStr">
+        <is>
+          <t>法务/侵权类</t>
+        </is>
+      </c>
+      <c r="B149" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C149" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D149" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 9 Sep 2026 14:40:23 +0000</t>
+        </is>
+      </c>
+      <c r="E149" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Seller Central &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F149" s="2" t="inlineStr">
+        <is>
+          <t>Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026</t>
+        </is>
+      </c>
+      <c r="G149" s="2" t="inlineStr"/>
+      <c r="H149" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Your Amazon.ca Fulfillment by Amazon Merchant Invoice for 8/2026
+ 96
+Hello,
+We are writing to inform you that your electronic Fulfillment by Amazon Merchant Invoice for the month of 8/2026 is now available in your Seller Central Account.
+To access your invoice, go to your Tax Document Library . In your Tax Document Library, you will be able to view, download or print your invoice.
+The Amazon Services Team
+ Monsieur/Madame Shen zhen shi wei hai zhong xin ke ji you xian,
+Nous vous écrivons pour vous informer que votre Facture Expédié Par Amazon pour le mois de 8/2026 est maintenant disponible dans votre compte Seller Central.
+Pour accéder à votre facture, rendez-vous sur votre compte Seller Central et veuillez accéder à la page Rapports &gt; Bibliothèque d'informations fiscales &gt; Factures des frais du vendeur.
+Dans votre compte Seller Central, vous pourrez afficher, télécharger ou imprimer votre facture.
+Pour toute question, contactez le Support Vendeur.
+Cordialement,
+Amazon.ca
+ Report an issue with this email
+ If you have any questions visit: Seller Central
+ To change your email preferences visit: Notification Preferences
+ We hope you found this message to be useful. However, if you'd </t>
         </is>
       </c>
     </row>
@@ -13869,7 +13867,7 @@
     <row r="262">
       <c r="A262" s="2" t="inlineStr">
         <is>
-          <t>法务/侵权类</t>
+          <t>货件/库存类</t>
         </is>
       </c>
       <c r="B262" s="2" t="inlineStr">
@@ -13884,84 +13882,22 @@
       </c>
       <c r="D262" s="2" t="inlineStr">
         <is>
-          <t>Mon, 17 Aug 2026 00:28:18 +0000</t>
+          <t>Tue, 8 Sep 2026 09:37:46 +0000</t>
         </is>
       </c>
       <c r="E262" s="2" t="inlineStr">
         <is>
-          <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
+          <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F262" s="2" t="inlineStr">
         <is>
-          <t>通过 Q4 活动拓展您的业务 — 尽早提报，节省费用</t>
+          <t>RE:[CASE 13247704742] Optimize Your Next EU FBA Shipment Based on
+ Inventory Health [A-AWD]</t>
         </is>
       </c>
       <c r="G262" s="2" t="inlineStr"/>
       <c r="H262" s="2" t="inlineStr">
-        <is>
-          <t>最大化您的 Q4 业绩
-尊敬的卖家，
-为 Q4 活动做好准备 — 为数百万消费者打造不容错过的优惠！今年，Prime 会员大促（PBDD）将与去年同期回归，随后是黑色星期五活动周（BFW）。通过尽早提交促销并确保充足库存，助力您的业务增长。
-早鸟折扣：如果您在截止日期前提报促销 — 黑色星期五活动周截止 9 月 5 日 — 您将获得每笔固定预付费的折扣：UK: £4, DE: €5, FR/IT/ES: €3。
-关键日期
-Prime 会员大促
-活动日期： 与去年同期
-提报截止日期 ：促销 – 2026 年 9 月 23 日，价格折扣 – 活动结束前 12 小时
-入库截止日期：EU – 9 月 9 日，UK – 2026 年 9 月 18 日
-黑色星期五活动周
-活动日期：2026 年 11 月 19–30 日
-提报截止日期 ：促销 – 2026 年 11 月 18 日，价格折扣 – 活动结束前 12 小时
-入库截止日期：EU – 10 月 21 日，UK – 2026 年 10 月 30 日
-提报您的促销 &gt; https://go.amazonsellerservices.com/e/229492/reate-ld-DC-EM-D506286903-Wk33/7z57nq4/6833682036/h/EwqOpQDRvyzkesi0h5nPpxusBKgPYvfx-x83USAM_lc
-&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="section" role="presentation" style="width:100%;"&gt;
-	&lt;tbody&gt;
-		&lt;tr&gt;
-			&lt;td align="center"&gt;
-			&lt;div role="none"&gt;
-&lt;!--[if(mso)|(IE)]&gt;
-&lt;table align="center" border="0" cellpadding="0" cellspacing="0" class="block-grid-outlook" style="width:600px;" width="600" &gt;
-&lt;tr&gt;
-&lt;td style="line-height:0px;font-size:0px;mso-line-height-rule:exactly;"&gt;&lt;![endif]--&gt;
-			&lt;div style="margin:0 auto;border-radius:0px;max-width:600px;"&gt;
-			&lt;table align="center" border="0" cellpadding="0" cellspacing="0" role="presentation" style="width:100%;border-</t>
-        </is>
-      </c>
-    </row>
-    <row r="263">
-      <c r="A263" s="2" t="inlineStr">
-        <is>
-          <t>货件/库存类</t>
-        </is>
-      </c>
-      <c r="B263" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C263" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D263" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 8 Sep 2026 09:37:46 +0000</t>
-        </is>
-      </c>
-      <c r="E263" s="2" t="inlineStr">
-        <is>
-          <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F263" s="2" t="inlineStr">
-        <is>
-          <t>RE:[CASE 13247704742] Optimize Your Next EU FBA Shipment Based on
- Inventory Health [A-AWD]</t>
-        </is>
-      </c>
-      <c r="G263" s="2" t="inlineStr"/>
-      <c r="H263" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 RE:[CASE 13247704742] Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -13977,39 +13913,39 @@
         </is>
       </c>
     </row>
-    <row r="264">
-      <c r="A264" s="2" t="inlineStr">
+    <row r="263">
+      <c r="A263" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B264" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C264" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D264" s="2" t="inlineStr">
+      <c r="B263" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C263" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D263" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 04:16:10 +0000</t>
         </is>
       </c>
-      <c r="E264" s="2" t="inlineStr">
+      <c r="E263" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F264" s="2" t="inlineStr">
+      <c r="F263" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-17</t>
         </is>
       </c>
-      <c r="G264" s="2" t="inlineStr"/>
-      <c r="H264" s="2" t="inlineStr">
+      <c r="G263" s="2" t="inlineStr"/>
+      <c r="H263" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14033,39 +13969,39 @@
         </is>
       </c>
     </row>
-    <row r="265">
-      <c r="A265" s="2" t="inlineStr">
+    <row r="264">
+      <c r="A264" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B265" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C265" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D265" s="2" t="inlineStr">
+      <c r="B264" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C264" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D264" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 03:24:10 +0000</t>
         </is>
       </c>
-      <c r="E265" s="2" t="inlineStr">
+      <c r="E264" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F265" s="2" t="inlineStr">
+      <c r="F264" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G265" s="2" t="inlineStr"/>
-      <c r="H265" s="2" t="inlineStr">
+      <c r="G264" s="2" t="inlineStr"/>
+      <c r="H264" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14088,39 +14024,39 @@
         </is>
       </c>
     </row>
-    <row r="266">
-      <c r="A266" s="2" t="inlineStr">
+    <row r="265">
+      <c r="A265" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B266" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C266" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D266" s="2" t="inlineStr">
+      <c r="B265" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C265" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D265" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 13:15:30 +0000</t>
         </is>
       </c>
-      <c r="E266" s="2" t="inlineStr">
+      <c r="E265" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F266" s="2" t="inlineStr">
+      <c r="F265" s="2" t="inlineStr">
         <is>
           <t>Stranded SKUs scheduled for automatic removal</t>
         </is>
       </c>
-      <c r="G266" s="2" t="inlineStr"/>
-      <c r="H266" s="2" t="inlineStr">
+      <c r="G265" s="2" t="inlineStr"/>
+      <c r="H265" s="2" t="inlineStr">
         <is>
           <t>96
 Stranded SKUs scheduled for automatic removal
@@ -14132,39 +14068,39 @@
         </is>
       </c>
     </row>
-    <row r="267">
-      <c r="A267" s="2" t="inlineStr">
+    <row r="266">
+      <c r="A266" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B267" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C267" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D267" s="2" t="inlineStr">
+      <c r="B266" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C266" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D266" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 04:57:59 +0000</t>
         </is>
       </c>
-      <c r="E267" s="2" t="inlineStr">
+      <c r="E266" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F267" s="2" t="inlineStr">
+      <c r="F266" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-10</t>
         </is>
       </c>
-      <c r="G267" s="2" t="inlineStr"/>
-      <c r="H267" s="2" t="inlineStr">
+      <c r="G266" s="2" t="inlineStr"/>
+      <c r="H266" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14187,39 +14123,39 @@
         </is>
       </c>
     </row>
-    <row r="268">
-      <c r="A268" s="2" t="inlineStr">
+    <row r="267">
+      <c r="A267" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B268" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C268" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D268" s="2" t="inlineStr">
+      <c r="B267" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C267" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D267" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 03:20:04 +0000</t>
         </is>
       </c>
-      <c r="E268" s="2" t="inlineStr">
+      <c r="E267" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F268" s="2" t="inlineStr">
+      <c r="F267" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G268" s="2" t="inlineStr"/>
-      <c r="H268" s="2" t="inlineStr">
+      <c r="G267" s="2" t="inlineStr"/>
+      <c r="H267" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14243,39 +14179,39 @@
         </is>
       </c>
     </row>
-    <row r="269">
-      <c r="A269" s="2" t="inlineStr">
+    <row r="268">
+      <c r="A268" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B269" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C269" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D269" s="2" t="inlineStr">
+      <c r="B268" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C268" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D268" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 04:59:41 +0000</t>
         </is>
       </c>
-      <c r="E269" s="2" t="inlineStr">
+      <c r="E268" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F269" s="2" t="inlineStr">
+      <c r="F268" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G269" s="2" t="inlineStr"/>
-      <c r="H269" s="2" t="inlineStr">
+      <c r="G268" s="2" t="inlineStr"/>
+      <c r="H268" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14299,39 +14235,39 @@
         </is>
       </c>
     </row>
-    <row r="270">
-      <c r="A270" s="2" t="inlineStr">
+    <row r="269">
+      <c r="A269" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B270" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C270" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D270" s="2" t="inlineStr">
+      <c r="B269" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C269" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D269" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 04:00:24 +0000</t>
         </is>
       </c>
-      <c r="E270" s="2" t="inlineStr">
+      <c r="E269" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F270" s="2" t="inlineStr">
+      <c r="F269" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-03</t>
         </is>
       </c>
-      <c r="G270" s="2" t="inlineStr"/>
-      <c r="H270" s="2" t="inlineStr">
+      <c r="G269" s="2" t="inlineStr"/>
+      <c r="H269" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14355,39 +14291,39 @@
         </is>
       </c>
     </row>
-    <row r="271">
-      <c r="A271" s="2" t="inlineStr">
+    <row r="270">
+      <c r="A270" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B271" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C271" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D271" s="2" t="inlineStr">
+      <c r="B270" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C270" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D270" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 03:18:20 +0000</t>
         </is>
       </c>
-      <c r="E271" s="2" t="inlineStr">
+      <c r="E270" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F271" s="2" t="inlineStr">
+      <c r="F270" s="2" t="inlineStr">
         <is>
           <t>Disposal order created for unsellable FBA inventory</t>
         </is>
       </c>
-      <c r="G271" s="2" t="inlineStr"/>
-      <c r="H271" s="2" t="inlineStr">
+      <c r="G270" s="2" t="inlineStr"/>
+      <c r="H270" s="2" t="inlineStr">
         <is>
           <t>96
 Automated Removals of Unfulfillable Inventory
@@ -14411,39 +14347,39 @@
         </is>
       </c>
     </row>
-    <row r="272">
-      <c r="A272" s="2" t="inlineStr">
+    <row r="271">
+      <c r="A271" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B272" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C272" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D272" s="2" t="inlineStr">
+      <c r="B271" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C271" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D271" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 03:06:19 +0000</t>
         </is>
       </c>
-      <c r="E272" s="2" t="inlineStr">
+      <c r="E271" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F272" s="2" t="inlineStr">
+      <c r="F271" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-03</t>
         </is>
       </c>
-      <c r="G272" s="2" t="inlineStr"/>
-      <c r="H272" s="2" t="inlineStr">
+      <c r="G271" s="2" t="inlineStr"/>
+      <c r="H271" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -14464,39 +14400,39 @@
         </is>
       </c>
     </row>
-    <row r="273">
-      <c r="A273" s="2" t="inlineStr">
+    <row r="272">
+      <c r="A272" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B273" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C273" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D273" s="2" t="inlineStr">
+      <c r="B272" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C272" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D272" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 20:05:47 +0000</t>
         </is>
       </c>
-      <c r="E273" s="2" t="inlineStr">
+      <c r="E272" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon Operations &lt;fba-noreply@amazon.lu&gt;</t>
         </is>
       </c>
-      <c r="F273" s="2" t="inlineStr">
+      <c r="F272" s="2" t="inlineStr">
         <is>
           <t>Your Amazon-Fulfilled Inventory</t>
         </is>
       </c>
-      <c r="G273" s="2" t="inlineStr"/>
-      <c r="H273" s="2" t="inlineStr">
+      <c r="G272" s="2" t="inlineStr"/>
+      <c r="H272" s="2" t="inlineStr">
         <is>
           <t>Dear Seller,
 We recently notified you about the removal of your listing(s) for the product(s) listed below due to a safety recall.
@@ -14512,39 +14448,39 @@
         </is>
       </c>
     </row>
-    <row r="274">
-      <c r="A274" s="2" t="inlineStr">
+    <row r="273">
+      <c r="A273" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B274" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C274" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D274" s="2" t="inlineStr">
+      <c r="B273" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C273" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D273" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 00:17:14 +0000</t>
         </is>
       </c>
-      <c r="E274" s="2" t="inlineStr">
+      <c r="E273" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F274" s="2" t="inlineStr">
+      <c r="F273" s="2" t="inlineStr">
         <is>
           <t>View your US Q3-2026 CSBA fee rate</t>
         </is>
       </c>
-      <c r="G274" s="2" t="inlineStr"/>
-      <c r="H274" s="2" t="inlineStr">
+      <c r="G273" s="2" t="inlineStr"/>
+      <c r="H273" s="2" t="inlineStr">
         <is>
           <t>96
  (Important) CSBA US Fee rate for Q3-2026
@@ -14574,39 +14510,39 @@
         </is>
       </c>
     </row>
-    <row r="275">
-      <c r="A275" s="2" t="inlineStr">
+    <row r="274">
+      <c r="A274" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B275" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C275" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D275" s="2" t="inlineStr">
+      <c r="B274" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C274" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D274" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 15:43:49 +0000</t>
         </is>
       </c>
-      <c r="E275" s="2" t="inlineStr">
+      <c r="E274" s="2" t="inlineStr">
         <is>
           <t>Amazon Seller Newsletter &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F275" s="2" t="inlineStr">
+      <c r="F274" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026</t>
         </is>
       </c>
-      <c r="G275" s="2" t="inlineStr"/>
-      <c r="H275" s="2" t="inlineStr">
+      <c r="G274" s="2" t="inlineStr"/>
+      <c r="H274" s="2" t="inlineStr">
         <is>
           <t>Seller News: August 2026
  96
@@ -14616,40 +14552,40 @@
         </is>
       </c>
     </row>
-    <row r="276">
-      <c r="A276" s="2" t="inlineStr">
+    <row r="275">
+      <c r="A275" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B276" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C276" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D276" s="2" t="inlineStr">
+      <c r="B275" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C275" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D275" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 14:03:19 +0000</t>
         </is>
       </c>
-      <c r="E276" s="2" t="inlineStr">
+      <c r="E275" s="2" t="inlineStr">
         <is>
           <t>Amazon Multichannel Fulfillment Team &lt;multichannelfulfillment@supplychain.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F276" s="2" t="inlineStr">
+      <c r="F275" s="2" t="inlineStr">
         <is>
           <t>Early access: Bring the trust of Prime to your ecommerce site with
  MCF</t>
         </is>
       </c>
-      <c r="G276" s="2" t="inlineStr"/>
-      <c r="H276" s="2" t="inlineStr">
+      <c r="G275" s="2" t="inlineStr"/>
+      <c r="H275" s="2" t="inlineStr">
         <is>
           <t>Early access: Bring the trust of Prime to your ecommerce site with MCF
 Hi there,

--- a/important_mails_2026-09-16.xlsx
+++ b/important_mails_2026-09-16.xlsx
@@ -490,7 +490,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>last7</t>
         </is>
       </c>
       <c r="C2" s="2" t="inlineStr">
@@ -533,12 +533,12 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>付款/资金类</t>
+          <t>店铺绩效类</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>today</t>
+          <t>last7</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
@@ -548,21 +548,357 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Wed, 16 Sep 2026 12:07:50 +0000</t>
+          <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Strategies built for sellers at your stage—plus $200 off</t>
+          <t>FBA reimbursement notification</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr"/>
       <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfillment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+- T</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B4" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>Sun, 13 Sep 2026 04:42:34 +0000</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 04:52:40 +0000</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 09:37:22 +0000</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfillment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+- T</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 05:39:06 +0000</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 09:08:38 +0000</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfillment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+- T</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>店铺绩效类</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 05:04:40 +0000</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>FBA reimbursement notification</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>96
+FBA reimbursement notification
+ You have a reimbursement activity
+ Hello from Fulfilment by Amazon,
+We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
+Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
+Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
+You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
+- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
+- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
+-</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 12:07:50 +0000</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>Strategies built for sellers at your stage—plus $200 off</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrvp/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
 [Secure your spot](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrvs/6889941143/h/MQuKVqSCTubvlftYjmZsRYwIhpcMmpopXweaNOtgp5c)
@@ -576,39 +912,440 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 15:16:31 +0000</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 09/15/26 15:11 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 430.18.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 14:49:51 +0000</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 09/15/26 14:49 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 232,19.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 13:38:38 +0000</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 09/15/26 13:38 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
+ 136.84.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 13:11:23 +0000</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>The Accelerate 2026 agenda got even better. See what's new.</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4gm/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
+[Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
+New content. Same packed lineup. More reasons to be there.
+The Amazon Accelerate 2026 agenda keeps getting better. We've added new sessions and experiences we think you’ll love.
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
+Here's what's new on the agenda:
+- AI tools you can use today
+New sessions on how to use AI-powered tools for listing creation, A+ Content optimization, and inventory planning—with step-by-step guidance you can apply immediately.
+- Brand building programs
+Learn how to use Brand Registry, A+ Content, and Brand Tailored Promotions to protect and grow your brand.
+- Account health essentials
+New workshops on proactively managing your account health, understanding policies, and staying in good standing—so you can focus on growing instead of troubleshooting.
+- W</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Sat, 12 Sep 2026 00:41:46 +0000</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement Attempted
+Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
+On 09/12/26 00:41 BST, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
+ 254.73.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To find out more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon store,
+Amazon Services
+Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Fri, 11 Sep 2026 14:52:08 +0000</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>Discover sessions built for growing businesses, and save $200</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrws/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
+[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrww/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
+Your next level starts here
+Amazon Accelerate is meant for sellers at every level and all stages of growth, from your first sale to your ten-thousandth. Last year, 4 out of 5 attendees left feeling more confident in growing their business.
+This September 22–24 in Seattle, Accelerate brings you sessions, networking, and 1:1 expert access designed to meet you where you are.
+For a limited time, use code FLASH200 at checkout to save $200 and register for just $399. This offer won't last, so don't wait.
+[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrww/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
+"We brought up our questions and challenges when signing up at the Seller Café, the SME has tremendous knowledge in her field and she did a deep dive into our Amazon account prior to the meeting and was totally prepared to a</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 12:33:05 +0000</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>Your payment is on the way</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ Congratulations! Your payment is on the way and will arrive soon.
+ Disbursement attempted
+Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
+On 09/10/26 12:27 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
+ 387.93.
+ If the amount is less than expected, here are a few questions to consider:
+ Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
+ Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
+To learn more about Payment Reports in Seller Central, please visit our official course.
+We wish you continued success!
+Thank you for selling in the Amazon Store,
+Amazon Services
+Help us improve your payment experience on Amaz</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>付款/资金类</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 12:27:50 +0000</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>Tu pago está en camino</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>96
+This title will display on mobile devices
+ ¡Enhorabuena! El pago está de camino y llegará pronto.
+ El pago está en camino
+Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
+El 09/10/26 12:27 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
+ 201,69.
+ Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
+ ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
+ ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
+Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
+Te deseamos un éx</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
         <is>
           <t>产品链接/合规类</t>
         </is>
       </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>today</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 07:08:09 +0000</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>"ppwr-cn-seller-compliance@amazon.com" &lt;ppwr-cn-seller-compliance@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号</t>
         </is>
       </c>
-      <c r="G4" s="2" t="inlineStr"/>
-      <c r="H4" s="2" t="inlineStr">
+      <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 12309992722] 需要采取行动：请向亚马逊提交您的EPR包装法注册号
@@ -635,39 +1372,194 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Submit proof of insurance by January 18 to avoid listing
+ deactivation</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
+ Hello,
+Submit proof of commercial liability insurance by January 18, 2027, to continue selling categories with enhanced safety listing requirements on Amazon.com.
+ To view your impacted products and categories, visit: Link to ASIN . Review the requirements and next steps below.
+ Why is proof of insurance required?
+ We are requiring proof of insurance because your listings in categories with enhanced safety require commercial liability insurance with a minimum coverage of $1 million per occurrence and in aggregate. Effective January 18, 2027, sellers with listings in these categories must maintain this coverage regardless of their gross proceeds. This requirement also applies to sellers who exceed USD $10,000 in gross proceeds in any month on Amazon.com, regardless of category.
+ To learn more, go to Commercial Liability Insurance Requirements .
+ How do I avoid listing deactivation?
+ Complete the following steps by January 18, 2027:
+- Get insurance: Obtain a commercial general, excess, or umbrella liability insurance policy with minimum coverage of $1</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Mon, 14 Sep 2026 05:40:35 +0000</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
+ A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
+        </is>
+      </c>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>96
+SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
+ Do not reply back to this e-mail!
+Hello,
+Thank you for submitting a document to the Chemical Safety Compliance Team.
+Your product is a kit/set/pack. A Safety Data Sheet is required for each possible hazardous product from the kit/set/pack, as indicated below:
+color acrylic paint;
+Ceramic clay
+● We already received a compliant documentation for "color acrylic paint"
+● The document uploaded for "Ceramic clay" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
+→ The SDS does not match the ( branding/manufacturer/logo of the product ):
+The manufacturer/brand/logo of the product on the SDS is "Eternity Commerce LTD" while the listing manufacturer/brand/logo of the product is "Roaxkois".
+Until we receive the entire valid documentation, for all the possible hazardous products from the kit/set/pack, the hazard warnings for your products may not appear on the ASIN's product detail page and your products may be rejected by some fulfillment centers.
+For guidance on Safety Data Sheet requirements, please refer to https</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Thu, 10 Sep 2026 15:50:06 +0000</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Submit product compliance documents to avoid listing removal</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Submit product compliance documents to avoid listing removal
+ Hello Weihai EU,
+ Your listings are at risk of removal due to missing Safety Data Sheets. Submit the required documentation by 2026-11-08 to continue selling these products. You can find examples of your at-risk listings at the bottom of this email.
+ Why is this happening?
+ We are taking this action because we identified hazardous products in your catalogue that require Safety Data Sheets (SDS). These documents are required by law and provide critical safety information about chemical products, including proper handling, storage and emergency procedures. This helps ensure the safety of our customers, employees and anyone who handles these products.
+ To learn more, go to our Requirements and FAQ for the sale of chemicals .
+ How do I continue to sell the affected products?
+ To avoid listing removal and continue selling these products, upload the Safety Data Sheets (SDS) for each of the affected products. Click the “View Compliance Requirements” button below to see all affected listings.
+ View Compliance Requirements
+ What was affected?
+ Reason
+ At-risk sales
+ B0GYPZ58JY
+ ASIN: B0GYPZ58JY
+ SKU: WH-TCJ-EU-0427-01
+ Hazard</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>today</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:36:30 +0000</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>Notificaciones de Seller Central (sin buzón electrónico) &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>Actualización de estado de mercancías peligrosas</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr">
+      <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Actualización de estado de mercancías peligrosas
@@ -690,39 +1582,39 @@
         </is>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>today</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:32:49 +0000</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>"Powiadomienia z Amazon Seller Central (nie odpowiadaj)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>Status materiałów niebezpiecznych (hazmat)</t>
         </is>
       </c>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr">
+      <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
  Status materiałów niebezpiecznych (hazmat)
@@ -745,39 +1637,39 @@
         </is>
       </c>
     </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>today</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
         <is>
           <t>Wed, 16 Sep 2026 01:02:50 +0000</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>"Notifiche di Amazon Seller Central (non rispondere)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>Aggiornamento dello stato delle merci pericolose</t>
         </is>
       </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr">
+      <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr">
         <is>
           <t>96
  Aggiornamento dello stato delle merci pericolose
@@ -800,903 +1692,10 @@
         </is>
       </c>
     </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>其他风险类</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>today</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 16 Sep 2026 01:31:48 +0000</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Dangerous goods (hazmat) status update</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr"/>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>96
- Dangerous goods (hazmat) status update
- Dangerous goods (hazmat) status update
- Hello from Fulfillment by Amazon,
- We are currently conducting a dangerous goods (hazmat) review of one or more of your products:
- CONFLICTING OR MISSING DG DOCUMENTATION
- ASIN
- Merchant SKU
- FNSKU
- Title
- B0HDVC3BVM
- WH-DE-811-WJJVINE-01
- Roaxkois Pelle mécanique télécommandée 3 en 1 pour Enfants de 6 à 12 Ans, télécommande 2,4 GHz, Accessoires métalliques, chenilles pivotantes à 680°. Idéale pour bac à Sable et Jeux extérieurs.
- B0HDVC3BVM
- WH-DE-911-WJJVINE-01
- Roaxkois Pelle mécanique télécommandée 3 en 1 pour Enfants de 6 à 12 Ans, télécommande 2,4 GHz, Accessoires métalliques, chenilles pivotantes à 680°. Idéale pour bac à Sable et Jeux extérieurs.
- Why this is happening
- We do not have enough dangerous goods information to correctly classify the above products, and until you provide the necessary information, the products will not be available for sale and you will not be able to send more units to Amazon fulfillment centers. We need you to provide a proper Safety Data Sheet (SDS) for each product listed above. You may submit an exemption sheet only if the product does not have an SDS and doe</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 15 Sep 2026 09:36:39 +0000</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr"/>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B10" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>Sun, 13 Sep 2026 04:42:34 +0000</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr"/>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B11" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 12 Sep 2026 04:52:40 +0000</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr"/>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B12" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 09:37:22 +0000</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr"/>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B13" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 05:39:06 +0000</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr"/>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B14" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 10 Sep 2026 09:08:38 +0000</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr"/>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfillment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfillment center. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.com/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.com/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
-- T</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>店铺绩效类</t>
-        </is>
-      </c>
-      <c r="B15" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C15" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D15" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 10 Sep 2026 05:04:40 +0000</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="inlineStr">
-        <is>
-          <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>FBA reimbursement notification</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>96
-FBA reimbursement notification
- You have a reimbursement activity
- Hello from Fulfilment by Amazon,
-We have initiated a reimbursement, a reimbursement reversal, or both due to recent activity on your selling account. No action is required from you.
-Reimbursements can be initiated for an issue that you notified us about or one that we identified at a fulfilment centre. A reimbursement reversal occurs when a reimbursement decision has been reviewed and changed. Reimbursement amounts are determined in accordance with the FBA inventory reimbursement policy ( https://sellercentral.amazon.co.uk/gp/help/external/200213130 ).
-Please note that it may take up to five business days for reimbursement transactions to appear in your seller account.
-You can find details on your reimbursement or reversal transaction in the Reimbursements report ( https://sellercentral.amazon.co.uk/reportcentral/REIMBURSEMENTS/0 ) in Seller Central:
-- In the Event Date drop-down menu, select a date range and click Generate report . You can use the date in the subject line of this email as a point of reference.
-- To identify inventory reimbursements and reversals, see the Quantity reimbursed [inventory] column.
--</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B16" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 15 Sep 2026 15:16:31 +0000</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 09/15/26 15:11 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 430.18.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B17" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C17" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D17" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 15 Sep 2026 14:49:51 +0000</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr"/>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 09/15/26 14:49 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 232,19.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 15 Sep 2026 13:38:38 +0000</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
-      <c r="H18" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 09/15/26 13:38 CEST, we initiated a transfer to your payment method (bank account ending in 229) in the amount of €
- 136.84.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims, or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees, and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B19" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D19" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 14 Sep 2026 13:11:23 +0000</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>The Accelerate 2026 agenda got even better. See what's new.</t>
-        </is>
-      </c>
-      <c r="G19" s="2" t="inlineStr"/>
-      <c r="H19" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4gm/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
-[Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
-New content. Same packed lineup. More reasons to be there.
-The Amazon Accelerate 2026 agenda keeps getting better. We've added new sessions and experiences we think you’ll love.
-[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4gq/6885907415/h/1g4K0sP-fwBdUvnQHTI9XLWTzXNhSmHYs6__l_Evdwk)
-Here's what's new on the agenda:
-- AI tools you can use today
-New sessions on how to use AI-powered tools for listing creation, A+ Content optimization, and inventory planning—with step-by-step guidance you can apply immediately.
-- Brand building programs
-Learn how to use Brand Registry, A+ Content, and Brand Tailored Promotions to protect and grow your brand.
-- Account health essentials
-New workshops on proactively managing your account health, understanding policies, and staying in good standing—so you can focus on growing instead of troubleshooting.
-- W</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B20" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C20" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>Sat, 12 Sep 2026 00:41:46 +0000</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G20" s="2" t="inlineStr"/>
-      <c r="H20" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement Attempted
-Congratulations Weihai EU! Your payment is on the way and will arrive within three to five days.
-On 09/12/26 00:41 BST, we initiated a transfer to your payment method (bank account ending in 191) in the amount of £
- 254.73.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To find out more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon store,
-Amazon Services
-Help us improve your payment experience on Ama</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B21" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D21" s="2" t="inlineStr">
-        <is>
-          <t>Fri, 11 Sep 2026 14:52:08 +0000</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F21" s="2" t="inlineStr">
-        <is>
-          <t>Discover sessions built for growing businesses, and save $200</t>
-        </is>
-      </c>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr">
-        <is>
-          <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-10/7z5qrws/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
-[Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrww/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
-Your next level starts here
-Amazon Accelerate is meant for sellers at every level and all stages of growth, from your first sale to your ten-thousandth. Last year, 4 out of 5 attendees left feeling more confident in growing their business.
-This September 22–24 in Seattle, Accelerate brings you sessions, networking, and 1:1 expert access designed to meet you where you are.
-For a limited time, use code FLASH200 at checkout to save $200 and register for just $399. This offer won't last, so don't wait.
-[Register now](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5qrww/6883537229/h/8hGIqk3myHUPoHwg1cA2VFOh0rQM9Qk9zX-mp3ce36Q)
-"We brought up our questions and challenges when signing up at the Seller Café, the SME has tremendous knowledge in her field and she did a deep dive into our Amazon account prior to the meeting and was totally prepared to a</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B22" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 10 Sep 2026 12:33:05 +0000</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>Your payment is on the way</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
-      <c r="H22" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- Congratulations! Your payment is on the way and will arrive soon.
- Disbursement attempted
-Congratulations Weihai CA! Your payment is on the way and will arrive within three to five days.
-On 09/10/26 12:27 EDT, we initiated a transfer to your payment method (bank account ending in 151) in the amount of CAD
- 387.93.
- If the amount is less than expected, here are a few questions to consider:
- Do you have an unavailable balance? Amazon might be reserving money to cover potential returns, claims or chargebacks from buyers. If this is the case, the closing balance in your Payment Report will display the unavailable balance that is reserved.
- Did your sales cover all fees and returns for this statement period? The payment amount reflects sales activities, selling fees and fees for promotions or services. We recommend reviewing your Payment Report under the Reports tab in Seller Central to understand your closing balance.
-To learn more about Payment Reports in Seller Central, please visit our official course.
-We wish you continued success!
-Thank you for selling in the Amazon Store,
-Amazon Services
-Help us improve your payment experience on Amaz</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>付款/资金类</t>
-        </is>
-      </c>
-      <c r="B23" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C23" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D23" s="2" t="inlineStr">
-        <is>
-          <t>Thu, 10 Sep 2026 12:27:50 +0000</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>Tu pago está en camino</t>
-        </is>
-      </c>
-      <c r="G23" s="2" t="inlineStr"/>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>96
-This title will display on mobile devices
- ¡Enhorabuena! El pago está de camino y llegará pronto.
- El pago está en camino
-Enhorabuena, Weihai EU. Tu pago está en camino y te llegará en un plazo de tres a cinco días.
-El 09/10/26 12:27 WEST, iniciamos una transferencia a tu método de pago (cuenta bancaria terminado en 229) por un importe de €
- 201,69.
- Si el importe es inferior a lo esperado, ten en cuenta las siguientes preguntas:
- ¿Tienes saldo no disponible en tu cuenta de vendedor? Puede que hayamos reservado algo de dinero para posibles devoluciones, reclamaciones o reversiones de cargo de clientes. En este caso, el saldo de cierre de tu informe de pagos te mostrará el saldo no disponible en reserva.
- ¿Cubren tus ventas las tarifas de Amazon y las devoluciones del periodo de liquidación? El importe del pago refleja las ventas que has hecho y las tarifas de venta aplicadas tanto a dichas ventas como a cualquier promoción o servicio que hayas utilizado. Te recomendamos que revises tu informe de pagos en "Informes" de Seller Central para conocer el saldo de cierre.
-Para más información sobre los informes de pagos en Seller Central, visita nuestro curso oficial.
-Te deseamos un éx</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B24" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C24" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D24" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 15 Sep 2026 20:32:42 +0000</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="inlineStr">
-        <is>
-          <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>Submit proof of insurance by January 18 to avoid listing
- deactivation</t>
-        </is>
-      </c>
-      <c r="G24" s="2" t="inlineStr"/>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>96
- Review your impacted products and categories and submit proof of insurance before January 18, 2027 to avoid listing deactivation.
- Hello,
-Submit proof of commercial liability insurance by January 18, 2027, to continue selling categories with enhanced safety listing requirements on Amazon.com.
- To view your impacted products and categories, visit: Link to ASIN . Review the requirements and next steps below.
- Why is proof of insurance required?
- We are requiring proof of insurance because your listings in categories with enhanced safety require commercial liability insurance with a minimum coverage of $1 million per occurrence and in aggregate. Effective January 18, 2027, sellers with listings in these categories must maintain this coverage regardless of their gross proceeds. This requirement also applies to sellers who exceed USD $10,000 in gross proceeds in any month on Amazon.com, regardless of category.
- To learn more, go to Commercial Liability Insurance Requirements .
- How do I avoid listing deactivation?
- Complete the following steps by January 18, 2027:
-- Get insurance: Obtain a commercial general, excess, or umbrella liability insurance policy with minimum coverage of $1</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B25" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D25" s="2" t="inlineStr">
-        <is>
-          <t>Mon, 14 Sep 2026 05:40:35 +0000</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="inlineStr">
-        <is>
-          <t>"cscompliance-docreview-seller@amazon.de" &lt;cscompliance-docreview-seller@amazon.de&gt;</t>
-        </is>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE:
- A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review</t>
-        </is>
-      </c>
-      <c r="G25" s="2" t="inlineStr"/>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>96
-SELLER: A1UYGOR4ZW45MU, ASIN: B0GYPZ58JY, MARKETPLACE: A1PA6795UKMFR9 - SPO - Seller Partner Outreach - Document Review
- Do not reply back to this e-mail!
-Hello,
-Thank you for submitting a document to the Chemical Safety Compliance Team.
-Your product is a kit/set/pack. A Safety Data Sheet is required for each possible hazardous product from the kit/set/pack, as indicated below:
-color acrylic paint;
-Ceramic clay
-● We already received a compliant documentation for "color acrylic paint"
-● The document uploaded for "Ceramic clay" is incomplete, inaccurate or otherwise conflicting, and cannot be used for classification. Specifically:
-→ The SDS does not match the ( branding/manufacturer/logo of the product ):
-The manufacturer/brand/logo of the product on the SDS is "Eternity Commerce LTD" while the listing manufacturer/brand/logo of the product is "Roaxkois".
-Until we receive the entire valid documentation, for all the possible hazardous products from the kit/set/pack, the hazard warnings for your products may not appear on the ASIN's product detail page and your products may be rejected by some fulfillment centers.
-For guidance on Safety Data Sheet requirements, please refer to https</t>
-        </is>
-      </c>
-    </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>产品链接/合规类</t>
+          <t>法务/侵权类</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
@@ -1711,7 +1710,7 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Thu, 10 Sep 2026 15:50:06 +0000</t>
+          <t>Tue, 15 Sep 2026 19:03:56 +0000</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
@@ -1721,115 +1720,11 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>Submit product compliance documents to avoid listing removal</t>
+          <t>Recover between 60-80%* from returns</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr"/>
       <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>96
- Submit product compliance documents to avoid listing removal
- Hello Weihai EU,
- Your listings are at risk of removal due to missing Safety Data Sheets. Submit the required documentation by 2026-11-08 to continue selling these products. You can find examples of your at-risk listings at the bottom of this email.
- Why is this happening?
- We are taking this action because we identified hazardous products in your catalogue that require Safety Data Sheets (SDS). These documents are required by law and provide critical safety information about chemical products, including proper handling, storage and emergency procedures. This helps ensure the safety of our customers, employees and anyone who handles these products.
- To learn more, go to our Requirements and FAQ for the sale of chemicals .
- How do I continue to sell the affected products?
- To avoid listing removal and continue selling these products, upload the Safety Data Sheets (SDS) for each of the affected products. Click the “View Compliance Requirements” button below to see all affected listings.
- View Compliance Requirements
- What was affected?
- Reason
- At-risk sales
- B0GYPZ58JY
- ASIN: B0GYPZ58JY
- SKU: WH-TCJ-EU-0427-01
- Hazard</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>产品链接/合规类</t>
-        </is>
-      </c>
-      <c r="B27" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D27" s="2" t="inlineStr">
-        <is>
-          <t>Wed, 9 Sep 2026 18:07:39 +0000</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>Submit product safety documentation to reactivate listings</t>
-        </is>
-      </c>
-      <c r="G27" s="2" t="inlineStr"/>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">96
- Submit product safety documentation to reactivate listings
- Hello Weihai CA,
- Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
- Why is this happening?
- We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
- The table at the end of this email provides product-specific compliance requirements.
- How do I reactivate my listings?
- To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
--
- If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
--
- If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>法务/侵权类</t>
-        </is>
-      </c>
-      <c r="B28" s="2" t="inlineStr">
-        <is>
-          <t>last7</t>
-        </is>
-      </c>
-      <c r="C28" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D28" s="2" t="inlineStr">
-        <is>
-          <t>Tue, 15 Sep 2026 19:03:56 +0000</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="inlineStr">
-        <is>
-          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
-        </is>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>Recover between 60-80%* from returns</t>
-        </is>
-      </c>
-      <c r="G28" s="2" t="inlineStr"/>
-      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
  We handle the grading and reselling. You keep control of pricing and recover value.
@@ -1852,39 +1747,39 @@
         </is>
       </c>
     </row>
-    <row r="29">
-      <c r="A29" s="2" t="inlineStr">
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B29" s="2" t="inlineStr">
+      <c r="B27" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 15:54:49 +0000</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>Parcel Tax for Austrian B2C orders</t>
         </is>
       </c>
-      <c r="G29" s="2" t="inlineStr"/>
-      <c r="H29" s="2" t="inlineStr">
+      <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr">
         <is>
           <t>Parcel Tax for Austrian B2C orders
  96
@@ -1895,39 +1790,39 @@
         </is>
       </c>
     </row>
-    <row r="30">
-      <c r="A30" s="2" t="inlineStr">
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B30" s="2" t="inlineStr">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C30" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 00:43:23 +0000</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>Votre paiement est en cours</t>
         </is>
       </c>
-      <c r="G30" s="2" t="inlineStr"/>
-      <c r="H30" s="2" t="inlineStr">
+      <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -1942,39 +1837,39 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="2" t="inlineStr">
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B31" s="2" t="inlineStr">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C31" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 14:08:42 +0000</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>通过 Q4 活动拓展您的业务 — 尽早提报，节省费用</t>
         </is>
       </c>
-      <c r="G31" s="2" t="inlineStr"/>
-      <c r="H31" s="2" t="inlineStr">
+      <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr">
         <is>
           <t>最大化您的 Q4 业绩
 尊敬的卖家，
@@ -2006,39 +1901,39 @@
         </is>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" s="2" t="inlineStr">
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
         <is>
           <t>法务/侵权类</t>
         </is>
       </c>
-      <c r="B32" s="2" t="inlineStr">
+      <c r="B30" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C32" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:39:41 +0000</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>"Comunicados de Amazon Seller Central (no responder)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>[Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon</t>
         </is>
       </c>
-      <c r="G32" s="2" t="inlineStr"/>
-      <c r="H32" s="2" t="inlineStr">
+      <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Amazon.es] Hemos suprimido uno o varios de tus listings de las búsquedas en la web de Amazon
@@ -2054,39 +1949,39 @@
         </is>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" s="2" t="inlineStr">
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B33" s="2" t="inlineStr">
+      <c r="B31" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C33" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
         <is>
           <t>Sat, 12 Sep 2026 04:18:39 +0000</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>Fulfilment by Amazon &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>Create FBA removal order by 2026-09-24</t>
         </is>
       </c>
-      <c r="G33" s="2" t="inlineStr"/>
-      <c r="H33" s="2" t="inlineStr">
+      <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr">
         <is>
           <t>96
 Automated removals of unfulfillable inventory
@@ -2109,40 +2004,40 @@
         </is>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
         <is>
           <t>货件/库存类</t>
         </is>
       </c>
-      <c r="B34" s="2" t="inlineStr">
+      <c r="B32" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C34" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
         <is>
           <t>Fri, 11 Sep 2026 09:43:34 +0000</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>"seller-coaching-m@amazon.com" &lt;seller-coaching-m@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>[Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA
  Shipment Based on Inventory Health [A-AWD]</t>
         </is>
       </c>
-      <c r="G34" s="2" t="inlineStr"/>
-      <c r="H34" s="2" t="inlineStr">
+      <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:13247704742]"Your Help Needed" Optimize Your Next EU FBA Shipment Based on Inventory Health [A-AWD]
@@ -2160,39 +2055,94 @@
         </is>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" s="2" t="inlineStr">
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B35" s="2" t="inlineStr">
+      <c r="B33" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C35" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 16 Sep 2026 01:31:48 +0000</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>"Amazon Seller Central Notifications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Dangerous goods (hazmat) status update</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>96
+ Dangerous goods (hazmat) status update
+ Dangerous goods (hazmat) status update
+ Hello from Fulfillment by Amazon,
+ We are currently conducting a dangerous goods (hazmat) review of one or more of your products:
+ CONFLICTING OR MISSING DG DOCUMENTATION
+ ASIN
+ Merchant SKU
+ FNSKU
+ Title
+ B0HDVC3BVM
+ WH-DE-811-WJJVINE-01
+ Roaxkois Pelle mécanique télécommandée 3 en 1 pour Enfants de 6 à 12 Ans, télécommande 2,4 GHz, Accessoires métalliques, chenilles pivotantes à 680°. Idéale pour bac à Sable et Jeux extérieurs.
+ B0HDVC3BVM
+ WH-DE-911-WJJVINE-01
+ Roaxkois Pelle mécanique télécommandée 3 en 1 pour Enfants de 6 à 12 Ans, télécommande 2,4 GHz, Accessoires métalliques, chenilles pivotantes à 680°. Idéale pour bac à Sable et Jeux extérieurs.
+ Why this is happening
+ We do not have enough dangerous goods information to correctly classify the above products, and until you provide the necessary information, the products will not be available for sale and you will not be able to send more units to Amazon fulfillment centers. We need you to provide a proper Safety Data Sheet (SDS) for each product listed above. You may submit an exemption sheet only if the product does not have an SDS and doe</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>其他风险类</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>last7</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
         <is>
           <t>Tue, 15 Sep 2026 10:27:49 +0800 (CST)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号管理 &lt;fli.lin@nbtscn.com&gt;</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>能标检测(NBTS）亚马逊DV-TRF号情况跟进</t>
         </is>
       </c>
-      <c r="G35" s="2" t="inlineStr"/>
-      <c r="H35" s="2" t="inlineStr">
+      <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr">
         <is>
           <t>尊敬的客户：
 您好！
@@ -2220,39 +2170,39 @@
         </is>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" s="2" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B36" s="2" t="inlineStr">
+      <c r="B35" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C36" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
         <is>
           <t>Mon, 14 Sep 2026 14:01:06 +0000</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>Redesigned Seller Central becomes default 24 Sep</t>
         </is>
       </c>
-      <c r="G36" s="2" t="inlineStr"/>
-      <c r="H36" s="2" t="inlineStr">
+      <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr">
         <is>
           <t>96
  Same powerful tools, built to grow with your business.
@@ -2267,40 +2217,40 @@
         </is>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" s="2" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
         <is>
           <t>其他风险类</t>
         </is>
       </c>
-      <c r="B37" s="2" t="inlineStr">
+      <c r="B36" s="2" t="inlineStr">
         <is>
           <t>last7</t>
         </is>
       </c>
-      <c r="C37" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
         <is>
           <t>Thu, 10 Sep 2026 03:24:54 +0000</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>"Amazon Seller Central Communications (Do Not Reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>[Amazon.fr] One or More of Your Amazon Listings Have Been Search
  Suppressed</t>
         </is>
       </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr">
         <is>
           <t>96
 [Amazon.fr] One or More of Your Amazon Listings Have Been Search Suppressed
@@ -2317,39 +2267,39 @@
         </is>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" s="2" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B38" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C38" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D38" s="2" t="inlineStr">
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 11:29:22 +0000</t>
         </is>
       </c>
-      <c r="E38" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F38" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (YHD3zckrc9)</t>
         </is>
       </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2369,39 +2319,39 @@
         </is>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" s="2" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B39" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C39" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D39" s="2" t="inlineStr">
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 09:22:19 +0000</t>
         </is>
       </c>
-      <c r="E39" s="2" t="inlineStr">
+      <c r="E38" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F39" s="2" t="inlineStr">
+      <c r="F38" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G39" s="2" t="inlineStr"/>
-      <c r="H39" s="2" t="inlineStr">
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2417,39 +2367,39 @@
         </is>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" s="2" t="inlineStr">
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B40" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C40" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D40" s="2" t="inlineStr">
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 04:57:55 +0000</t>
         </is>
       </c>
-      <c r="E40" s="2" t="inlineStr">
+      <c r="E39" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F40" s="2" t="inlineStr">
+      <c r="F39" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G40" s="2" t="inlineStr"/>
-      <c r="H40" s="2" t="inlineStr">
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2465,39 +2415,39 @@
         </is>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" s="2" t="inlineStr">
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B41" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C41" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D41" s="2" t="inlineStr">
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 11:28:14 +0000</t>
         </is>
       </c>
-      <c r="E41" s="2" t="inlineStr">
+      <c r="E40" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F41" s="2" t="inlineStr">
+      <c r="F40" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (pWbU6lC/+G)</t>
         </is>
       </c>
-      <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2517,39 +2467,39 @@
         </is>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" s="2" t="inlineStr">
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B42" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C42" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D42" s="2" t="inlineStr">
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
         <is>
           <t>Mon, 7 Sep 2026 04:54:29 +0000</t>
         </is>
       </c>
-      <c r="E42" s="2" t="inlineStr">
+      <c r="E41" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F42" s="2" t="inlineStr">
+      <c r="F41" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G42" s="2" t="inlineStr"/>
-      <c r="H42" s="2" t="inlineStr">
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2565,39 +2515,39 @@
         </is>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B43" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D43" s="2" t="inlineStr">
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 04:38:47 +0000</t>
         </is>
       </c>
-      <c r="E43" s="2" t="inlineStr">
+      <c r="E42" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F43" s="2" t="inlineStr">
+      <c r="F42" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G43" s="2" t="inlineStr"/>
-      <c r="H43" s="2" t="inlineStr">
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2613,39 +2563,39 @@
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" s="2" t="inlineStr">
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B44" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D44" s="2" t="inlineStr">
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 09:20:41 +0000</t>
         </is>
       </c>
-      <c r="E44" s="2" t="inlineStr">
+      <c r="E43" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F44" s="2" t="inlineStr">
+      <c r="F43" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G44" s="2" t="inlineStr"/>
-      <c r="H44" s="2" t="inlineStr">
+      <c r="G43" s="2" t="inlineStr"/>
+      <c r="H43" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2661,39 +2611,39 @@
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" s="2" t="inlineStr">
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B45" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C45" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D45" s="2" t="inlineStr">
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 17:54:07 +0000</t>
         </is>
       </c>
-      <c r="E45" s="2" t="inlineStr">
+      <c r="E44" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F45" s="2" t="inlineStr">
+      <c r="F44" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (4rjrNkqMZx)</t>
         </is>
       </c>
-      <c r="G45" s="2" t="inlineStr"/>
-      <c r="H45" s="2" t="inlineStr">
+      <c r="G44" s="2" t="inlineStr"/>
+      <c r="H44" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2713,39 +2663,39 @@
         </is>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" s="2" t="inlineStr">
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B46" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C46" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D46" s="2" t="inlineStr">
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 05:00:38 +0000</t>
         </is>
       </c>
-      <c r="E46" s="2" t="inlineStr">
+      <c r="E45" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F46" s="2" t="inlineStr">
+      <c r="F45" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G46" s="2" t="inlineStr"/>
-      <c r="H46" s="2" t="inlineStr">
+      <c r="G45" s="2" t="inlineStr"/>
+      <c r="H45" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2761,39 +2711,39 @@
         </is>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" s="2" t="inlineStr">
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B47" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C47" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D47" s="2" t="inlineStr">
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 10:49:16 +0000</t>
         </is>
       </c>
-      <c r="E47" s="2" t="inlineStr">
+      <c r="E46" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F47" s="2" t="inlineStr">
+      <c r="F46" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (j2jHyzbiUU)</t>
         </is>
       </c>
-      <c r="G47" s="2" t="inlineStr"/>
-      <c r="H47" s="2" t="inlineStr">
+      <c r="G46" s="2" t="inlineStr"/>
+      <c r="H46" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2813,39 +2763,39 @@
         </is>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" s="2" t="inlineStr">
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B48" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C48" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D48" s="2" t="inlineStr">
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
         <is>
           <t>Wed, 2 Sep 2026 04:50:31 +0000</t>
         </is>
       </c>
-      <c r="E48" s="2" t="inlineStr">
+      <c r="E47" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F48" s="2" t="inlineStr">
+      <c r="F47" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr">
+      <c r="G47" s="2" t="inlineStr"/>
+      <c r="H47" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -2861,39 +2811,39 @@
         </is>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" s="2" t="inlineStr">
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B49" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C49" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D49" s="2" t="inlineStr">
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 19:31:35 +0000</t>
         </is>
       </c>
-      <c r="E49" s="2" t="inlineStr">
+      <c r="E48" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F49" s="2" t="inlineStr">
+      <c r="F48" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (TrF4EN0N6o)</t>
         </is>
       </c>
-      <c r="G49" s="2" t="inlineStr"/>
-      <c r="H49" s="2" t="inlineStr">
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -2918,39 +2868,39 @@
         </is>
       </c>
     </row>
-    <row r="50">
-      <c r="A50" s="2" t="inlineStr">
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B50" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D50" s="2" t="inlineStr">
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:06:42 +0000</t>
         </is>
       </c>
-      <c r="E50" s="2" t="inlineStr">
+      <c r="E49" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F50" s="2" t="inlineStr">
+      <c r="F49" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G50" s="2" t="inlineStr"/>
-      <c r="H50" s="2" t="inlineStr">
+      <c r="G49" s="2" t="inlineStr"/>
+      <c r="H49" s="2" t="inlineStr">
         <is>
           <t>96
 [Case ID:21758925371]*Your Case Resolved* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -2963,39 +2913,39 @@
         </is>
       </c>
     </row>
-    <row r="51">
-      <c r="A51" s="2" t="inlineStr">
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B51" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D51" s="2" t="inlineStr">
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 05:00:11 +0000</t>
         </is>
       </c>
-      <c r="E51" s="2" t="inlineStr">
+      <c r="E50" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F51" s="2" t="inlineStr">
+      <c r="F50" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G51" s="2" t="inlineStr"/>
-      <c r="H51" s="2" t="inlineStr">
+      <c r="G50" s="2" t="inlineStr"/>
+      <c r="H50" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3011,39 +2961,39 @@
         </is>
       </c>
     </row>
-    <row r="52">
-      <c r="A52" s="2" t="inlineStr">
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B52" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C52" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D52" s="2" t="inlineStr">
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
         <is>
           <t>Sun, 30 Aug 2026 14:03:08 +0000</t>
         </is>
       </c>
-      <c r="E52" s="2" t="inlineStr">
+      <c r="E51" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F52" s="2" t="inlineStr">
+      <c r="F51" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G52" s="2" t="inlineStr"/>
-      <c r="H52" s="2" t="inlineStr">
+      <c r="G51" s="2" t="inlineStr"/>
+      <c r="H51" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3064,39 +3014,39 @@
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" s="2" t="inlineStr">
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B53" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C53" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D53" s="2" t="inlineStr">
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 04:40:08 +0000</t>
         </is>
       </c>
-      <c r="E53" s="2" t="inlineStr">
+      <c r="E52" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F53" s="2" t="inlineStr">
+      <c r="F52" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G53" s="2" t="inlineStr"/>
-      <c r="H53" s="2" t="inlineStr">
+      <c r="G52" s="2" t="inlineStr"/>
+      <c r="H52" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3112,39 +3062,39 @@
         </is>
       </c>
     </row>
-    <row r="54">
-      <c r="A54" s="2" t="inlineStr">
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B54" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C54" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D54" s="2" t="inlineStr">
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 16:34:35 +0000</t>
         </is>
       </c>
-      <c r="E54" s="2" t="inlineStr">
+      <c r="E53" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F54" s="2" t="inlineStr">
+      <c r="F53" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0QNxXwzJgp)</t>
         </is>
       </c>
-      <c r="G54" s="2" t="inlineStr"/>
-      <c r="H54" s="2" t="inlineStr">
+      <c r="G53" s="2" t="inlineStr"/>
+      <c r="H53" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3164,39 +3114,39 @@
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" s="2" t="inlineStr">
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B55" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C55" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D55" s="2" t="inlineStr">
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 15:00:25 +0000</t>
         </is>
       </c>
-      <c r="E55" s="2" t="inlineStr">
+      <c r="E54" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F55" s="2" t="inlineStr">
+      <c r="F54" s="2" t="inlineStr">
         <is>
           <t>[Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G55" s="2" t="inlineStr"/>
-      <c r="H55" s="2" t="inlineStr">
+      <c r="G54" s="2" t="inlineStr"/>
+      <c r="H54" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 [Case ID:21758925371]*Your Help Needed* You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -3210,39 +3160,39 @@
         </is>
       </c>
     </row>
-    <row r="56">
-      <c r="A56" s="2" t="inlineStr">
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B56" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C56" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D56" s="2" t="inlineStr">
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 09:22:31 +0000</t>
         </is>
       </c>
-      <c r="E56" s="2" t="inlineStr">
+      <c r="E55" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F56" s="2" t="inlineStr">
+      <c r="F55" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G56" s="2" t="inlineStr"/>
-      <c r="H56" s="2" t="inlineStr">
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3258,39 +3208,39 @@
         </is>
       </c>
     </row>
-    <row r="57">
-      <c r="A57" s="2" t="inlineStr">
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B57" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C57" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D57" s="2" t="inlineStr">
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
         <is>
           <t>Fri, 28 Aug 2026 04:53:03 +0000</t>
         </is>
       </c>
-      <c r="E57" s="2" t="inlineStr">
+      <c r="E56" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F57" s="2" t="inlineStr">
+      <c r="F56" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr"/>
-      <c r="H57" s="2" t="inlineStr">
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3306,39 +3256,39 @@
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="A58" s="2" t="inlineStr">
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B58" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D58" s="2" t="inlineStr">
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 05:02:47 +0000</t>
         </is>
       </c>
-      <c r="E58" s="2" t="inlineStr">
+      <c r="E57" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F58" s="2" t="inlineStr">
+      <c r="F57" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G58" s="2" t="inlineStr"/>
-      <c r="H58" s="2" t="inlineStr">
+      <c r="G57" s="2" t="inlineStr"/>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3354,39 +3304,39 @@
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="A59" s="2" t="inlineStr">
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B59" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D59" s="2" t="inlineStr">
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D58" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 23:58:41 +0000</t>
         </is>
       </c>
-      <c r="E59" s="2" t="inlineStr">
+      <c r="E58" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F59" s="2" t="inlineStr">
+      <c r="F58" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (0Bix9UfQE5)</t>
         </is>
       </c>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr">
+      <c r="G58" s="2" t="inlineStr"/>
+      <c r="H58" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3406,39 +3356,39 @@
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="A60" s="2" t="inlineStr">
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B60" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D60" s="2" t="inlineStr">
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 15:00:02 +0000</t>
         </is>
       </c>
-      <c r="E60" s="2" t="inlineStr">
+      <c r="E59" s="2" t="inlineStr">
         <is>
           <t>"dg-seller-enrollment@amazon.com" &lt;dg-seller-enrollment@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F60" s="2" t="inlineStr">
+      <c r="F59" s="2" t="inlineStr">
         <is>
           <t>RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US</t>
         </is>
       </c>
-      <c r="G60" s="2" t="inlineStr"/>
-      <c r="H60" s="2" t="inlineStr">
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr">
         <is>
           <t>96
 RE:[CASE 21758925371] You’re invited to the Dangerous Goods (Hazmat) Program US
@@ -3449,39 +3399,39 @@
         </is>
       </c>
     </row>
-    <row r="61">
-      <c r="A61" s="2" t="inlineStr">
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B61" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C61" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D61" s="2" t="inlineStr">
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D60" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 04:58:09 +0000</t>
         </is>
       </c>
-      <c r="E61" s="2" t="inlineStr">
+      <c r="E60" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F61" s="2" t="inlineStr">
+      <c r="F60" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr">
+      <c r="G60" s="2" t="inlineStr"/>
+      <c r="H60" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3497,39 +3447,39 @@
         </is>
       </c>
     </row>
-    <row r="62">
-      <c r="A62" s="2" t="inlineStr">
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B62" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C62" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D62" s="2" t="inlineStr">
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 18:49:27 +0000</t>
         </is>
       </c>
-      <c r="E62" s="2" t="inlineStr">
+      <c r="E61" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F62" s="2" t="inlineStr">
+      <c r="F61" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (qO7a7il03F)</t>
         </is>
       </c>
-      <c r="G62" s="2" t="inlineStr"/>
-      <c r="H62" s="2" t="inlineStr">
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3549,39 +3499,39 @@
         </is>
       </c>
     </row>
-    <row r="63">
-      <c r="A63" s="2" t="inlineStr">
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B63" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D63" s="2" t="inlineStr">
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D62" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:33:42 +0000</t>
         </is>
       </c>
-      <c r="E63" s="2" t="inlineStr">
+      <c r="E62" s="2" t="inlineStr">
         <is>
           <t>"Amazon.com" &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F63" s="2" t="inlineStr">
+      <c r="F62" s="2" t="inlineStr">
         <is>
           <t>Your FBA request is complete (aVWN9vWwFe)</t>
         </is>
       </c>
-      <c r="G63" s="2" t="inlineStr"/>
-      <c r="H63" s="2" t="inlineStr">
+      <c r="G62" s="2" t="inlineStr"/>
+      <c r="H62" s="2" t="inlineStr">
         <is>
           <t>Greetings from Amazon.com
 We thought you'd like to know that we have completed your destroy request.
@@ -3601,39 +3551,39 @@
         </is>
       </c>
     </row>
-    <row r="64">
-      <c r="A64" s="2" t="inlineStr">
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B64" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C64" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D64" s="2" t="inlineStr">
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 05:00:58 +0000</t>
         </is>
       </c>
-      <c r="E64" s="2" t="inlineStr">
+      <c r="E63" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F64" s="2" t="inlineStr">
+      <c r="F63" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G64" s="2" t="inlineStr"/>
-      <c r="H64" s="2" t="inlineStr">
+      <c r="G63" s="2" t="inlineStr"/>
+      <c r="H63" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3649,39 +3599,39 @@
         </is>
       </c>
     </row>
-    <row r="65">
-      <c r="A65" s="2" t="inlineStr">
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B65" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C65" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D65" s="2" t="inlineStr">
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:55:04 +0000</t>
         </is>
       </c>
-      <c r="E65" s="2" t="inlineStr">
+      <c r="E64" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F65" s="2" t="inlineStr">
+      <c r="F64" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G65" s="2" t="inlineStr"/>
-      <c r="H65" s="2" t="inlineStr">
+      <c r="G64" s="2" t="inlineStr"/>
+      <c r="H64" s="2" t="inlineStr">
         <is>
           <t>96
 Balance paid on your Amazon seller account
@@ -3704,39 +3654,39 @@
         </is>
       </c>
     </row>
-    <row r="66">
-      <c r="A66" s="2" t="inlineStr">
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B66" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C66" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D66" s="2" t="inlineStr">
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 14:36:21 +0000</t>
         </is>
       </c>
-      <c r="E66" s="2" t="inlineStr">
+      <c r="E65" s="2" t="inlineStr">
         <is>
           <t>"Amazon.co.uk" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F66" s="2" t="inlineStr">
+      <c r="F65" s="2" t="inlineStr">
         <is>
           <t>Balance paid on your Amazon seller account</t>
         </is>
       </c>
-      <c r="G66" s="2" t="inlineStr"/>
-      <c r="H66" s="2" t="inlineStr">
+      <c r="G65" s="2" t="inlineStr"/>
+      <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 Balance paid on your Amazon seller account
@@ -3754,39 +3704,39 @@
         </is>
       </c>
     </row>
-    <row r="67">
-      <c r="A67" s="2" t="inlineStr">
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B67" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C67" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D67" s="2" t="inlineStr">
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
         <is>
           <t>Sun, 23 Aug 2026 04:55:13 +0000</t>
         </is>
       </c>
-      <c r="E67" s="2" t="inlineStr">
+      <c r="E66" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F67" s="2" t="inlineStr">
+      <c r="F66" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr">
+      <c r="G66" s="2" t="inlineStr"/>
+      <c r="H66" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3802,39 +3752,39 @@
         </is>
       </c>
     </row>
-    <row r="68">
-      <c r="A68" s="2" t="inlineStr">
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B68" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D68" s="2" t="inlineStr">
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 03:28:54 +0000</t>
         </is>
       </c>
-      <c r="E68" s="2" t="inlineStr">
+      <c r="E67" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F68" s="2" t="inlineStr">
+      <c r="F67" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G68" s="2" t="inlineStr"/>
-      <c r="H68" s="2" t="inlineStr">
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -3850,39 +3800,39 @@
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="A69" s="2" t="inlineStr">
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B69" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D69" s="2" t="inlineStr">
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D68" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 16:10:20 +0000</t>
         </is>
       </c>
-      <c r="E69" s="2" t="inlineStr">
+      <c r="E68" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F69" s="2" t="inlineStr">
+      <c r="F68" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G69" s="2" t="inlineStr"/>
-      <c r="H69" s="2" t="inlineStr">
+      <c r="G68" s="2" t="inlineStr"/>
+      <c r="H68" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3903,39 +3853,39 @@
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="A70" s="2" t="inlineStr">
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B70" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D70" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 15:24:40 +0000</t>
         </is>
       </c>
-      <c r="E70" s="2" t="inlineStr">
+      <c r="E69" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F70" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G70" s="2" t="inlineStr"/>
-      <c r="H70" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr"/>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -3956,39 +3906,39 @@
         </is>
       </c>
     </row>
-    <row r="71">
-      <c r="A71" s="2" t="inlineStr">
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B71" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D71" s="2" t="inlineStr">
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D70" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 04:58:18 +0000</t>
         </is>
       </c>
-      <c r="E71" s="2" t="inlineStr">
+      <c r="E70" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F71" s="2" t="inlineStr">
+      <c r="F70" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G71" s="2" t="inlineStr"/>
-      <c r="H71" s="2" t="inlineStr">
+      <c r="G70" s="2" t="inlineStr"/>
+      <c r="H70" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4004,39 +3954,39 @@
         </is>
       </c>
     </row>
-    <row r="72">
-      <c r="A72" s="2" t="inlineStr">
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B72" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D72" s="2" t="inlineStr">
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
         <is>
           <t>Wed, 19 Aug 2026 16:12:03 +0000</t>
         </is>
       </c>
-      <c r="E72" s="2" t="inlineStr">
+      <c r="E71" s="2" t="inlineStr">
         <is>
           <t>Fulfillment by Amazon Operations &lt;fba-noreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F72" s="2" t="inlineStr">
+      <c r="F71" s="2" t="inlineStr">
         <is>
           <t>Automated unfulfillable FBA inventory removal notification</t>
         </is>
       </c>
-      <c r="G72" s="2" t="inlineStr"/>
-      <c r="H72" s="2" t="inlineStr">
+      <c r="G71" s="2" t="inlineStr"/>
+      <c r="H71" s="2" t="inlineStr">
         <is>
           <t>96
  Hello Weihai US,
@@ -4057,39 +4007,39 @@
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="A73" s="2" t="inlineStr">
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
         <is>
           <t>店铺绩效类</t>
         </is>
       </c>
-      <c r="B73" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C73" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D73" s="2" t="inlineStr">
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D72" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 05:03:01 +0000</t>
         </is>
       </c>
-      <c r="E73" s="2" t="inlineStr">
+      <c r="E72" s="2" t="inlineStr">
         <is>
           <t>"Fulfillment by Amazon (Do not reply)" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F73" s="2" t="inlineStr">
+      <c r="F72" s="2" t="inlineStr">
         <is>
           <t>FBA reimbursement notification</t>
         </is>
       </c>
-      <c r="G73" s="2" t="inlineStr"/>
-      <c r="H73" s="2" t="inlineStr">
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
         <is>
           <t>96
 FBA reimbursement notification
@@ -4105,39 +4055,39 @@
         </is>
       </c>
     </row>
-    <row r="74">
-      <c r="A74" s="2" t="inlineStr">
+    <row r="73">
+      <c r="A73" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B74" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C74" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D74" s="2" t="inlineStr">
+      <c r="B73" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C73" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D73" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 14:22:12 +0000</t>
         </is>
       </c>
-      <c r="E74" s="2" t="inlineStr">
+      <c r="E73" s="2" t="inlineStr">
         <is>
           <t>Amazon Payments Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F74" s="2" t="inlineStr">
+      <c r="F73" s="2" t="inlineStr">
         <is>
           <t>Rettifica del saldo negativo nei tuoi account</t>
         </is>
       </c>
-      <c r="G74" s="2" t="inlineStr"/>
-      <c r="H74" s="2" t="inlineStr">
+      <c r="G73" s="2" t="inlineStr"/>
+      <c r="H73" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4161,39 +4111,39 @@
         </is>
       </c>
     </row>
-    <row r="75">
-      <c r="A75" s="2" t="inlineStr">
+    <row r="74">
+      <c r="A74" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B75" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C75" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D75" s="2" t="inlineStr">
+      <c r="B74" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C74" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D74" s="2" t="inlineStr">
         <is>
           <t>Wed, 9 Sep 2026 13:24:25 +0000</t>
         </is>
       </c>
-      <c r="E75" s="2" t="inlineStr">
+      <c r="E74" s="2" t="inlineStr">
         <is>
           <t>Sell with Amazon &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F75" s="2" t="inlineStr">
+      <c r="F74" s="2" t="inlineStr">
         <is>
           <t>New sessions on AI, brand building, and account health</t>
         </is>
       </c>
-      <c r="G75" s="2" t="inlineStr"/>
-      <c r="H75" s="2" t="inlineStr">
+      <c r="G74" s="2" t="inlineStr"/>
+      <c r="H74" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-04/7z5l4fj/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5l4fm/6879091625/h/N9M90HPlPpU67n4uE_mKTweCIMAyiYf9R4WAB4ShsLU)
@@ -4209,39 +4159,39 @@
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="A76" s="2" t="inlineStr">
+    <row r="75">
+      <c r="A75" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B76" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C76" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D76" s="2" t="inlineStr">
+      <c r="B75" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C75" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D75" s="2" t="inlineStr">
         <is>
           <t>Tue, 8 Sep 2026 12:29:09 +0000</t>
         </is>
       </c>
-      <c r="E76" s="2" t="inlineStr">
+      <c r="E75" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F76" s="2" t="inlineStr">
+      <c r="F75" s="2" t="inlineStr">
         <is>
           <t>Grow your Amazon business this September—$200 off registration</t>
         </is>
       </c>
-      <c r="G76" s="2" t="inlineStr"/>
-      <c r="H76" s="2" t="inlineStr">
+      <c r="G75" s="2" t="inlineStr"/>
+      <c r="H75" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmdj/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmdm/6877034516/h/rztcP4y8gTis_yypujjYm1jG3dK9ZVpI_qeU8WzLMjQ)
@@ -4256,39 +4206,39 @@
         </is>
       </c>
     </row>
-    <row r="77">
-      <c r="A77" s="2" t="inlineStr">
+    <row r="76">
+      <c r="A76" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B77" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D77" s="2" t="inlineStr">
+      <c r="B76" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C76" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D76" s="2" t="inlineStr">
         <is>
           <t>Sun, 6 Sep 2026 13:43:26 +0000</t>
         </is>
       </c>
-      <c r="E77" s="2" t="inlineStr">
+      <c r="E76" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F77" s="2" t="inlineStr">
+      <c r="F76" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G77" s="2" t="inlineStr"/>
-      <c r="H77" s="2" t="inlineStr">
+      <c r="G76" s="2" t="inlineStr"/>
+      <c r="H76" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4308,39 +4258,39 @@
         </is>
       </c>
     </row>
-    <row r="78">
-      <c r="A78" s="2" t="inlineStr">
+    <row r="77">
+      <c r="A77" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B78" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C78" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D78" s="2" t="inlineStr">
+      <c r="B77" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C77" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D77" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 14:14:20 +0000</t>
         </is>
       </c>
-      <c r="E78" s="2" t="inlineStr">
+      <c r="E77" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F78" s="2" t="inlineStr">
+      <c r="F77" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G78" s="2" t="inlineStr"/>
-      <c r="H78" s="2" t="inlineStr">
+      <c r="G77" s="2" t="inlineStr"/>
+      <c r="H77" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -4364,39 +4314,39 @@
         </is>
       </c>
     </row>
-    <row r="79">
-      <c r="A79" s="2" t="inlineStr">
+    <row r="78">
+      <c r="A78" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B79" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C79" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D79" s="2" t="inlineStr">
+      <c r="B78" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C78" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D78" s="2" t="inlineStr">
         <is>
           <t>Sat, 5 Sep 2026 12:11:55 +0000</t>
         </is>
       </c>
-      <c r="E79" s="2" t="inlineStr">
+      <c r="E78" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F79" s="2" t="inlineStr">
+      <c r="F78" s="2" t="inlineStr">
         <is>
           <t>1:1 expert access, new AI tools, and $200 off—register now</t>
         </is>
       </c>
-      <c r="G79" s="2" t="inlineStr"/>
-      <c r="H79" s="2" t="inlineStr">
+      <c r="G78" s="2" t="inlineStr"/>
+      <c r="H78" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-09-03/7z5kmcf/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5kmcj/6873229782/h/qYVDW02XHhfOyfe1KqLK6R5PsXDPD3YirAthddzc8II)
@@ -4412,40 +4362,40 @@
         </is>
       </c>
     </row>
-    <row r="80">
-      <c r="A80" s="2" t="inlineStr">
+    <row r="79">
+      <c r="A79" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B80" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C80" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D80" s="2" t="inlineStr">
+      <c r="B79" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C79" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D79" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 15:50:39 +0000</t>
         </is>
       </c>
-      <c r="E80" s="2" t="inlineStr">
+      <c r="E79" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F80" s="2" t="inlineStr">
+      <c r="F79" s="2" t="inlineStr">
         <is>
           <t>A note from Katie Scott: Your spot at Amazon Accelerate 2026 is
  waiting</t>
         </is>
       </c>
-      <c r="G80" s="2" t="inlineStr"/>
-      <c r="H80" s="2" t="inlineStr">
+      <c r="G79" s="2" t="inlineStr"/>
+      <c r="H79" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj9l/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj9p/6869623185/h/t49nmPjAcWA0AwhOnCq47cStxvNE4bo5hge57UVyO-E)
@@ -4459,39 +4409,39 @@
         </is>
       </c>
     </row>
-    <row r="81">
-      <c r="A81" s="2" t="inlineStr">
+    <row r="80">
+      <c r="A80" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B81" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C81" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D81" s="2" t="inlineStr">
+      <c r="B80" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C80" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D80" s="2" t="inlineStr">
         <is>
           <t>Thu, 3 Sep 2026 14:51:26 +0000</t>
         </is>
       </c>
-      <c r="E81" s="2" t="inlineStr">
+      <c r="E80" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F81" s="2" t="inlineStr">
+      <c r="F80" s="2" t="inlineStr">
         <is>
           <t>Twoja płatność jest już w drodze</t>
         </is>
       </c>
-      <c r="G81" s="2" t="inlineStr"/>
-      <c r="H81" s="2" t="inlineStr">
+      <c r="G80" s="2" t="inlineStr"/>
+      <c r="H80" s="2" t="inlineStr">
         <is>
           <t>96
 Ten tytuł będzie wyświetlany na urządzeniach mobilnych
@@ -4507,39 +4457,39 @@
         </is>
       </c>
     </row>
-    <row r="82">
-      <c r="A82" s="2" t="inlineStr">
+    <row r="81">
+      <c r="A81" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B82" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C82" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D82" s="2" t="inlineStr">
+      <c r="B81" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C81" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D81" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:50:35 +0000</t>
         </is>
       </c>
-      <c r="E82" s="2" t="inlineStr">
+      <c r="E81" s="2" t="inlineStr">
         <is>
           <t>The Amazon Services team &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F82" s="2" t="inlineStr">
+      <c r="F81" s="2" t="inlineStr">
         <is>
           <t>Download your China tax report for October - December 2025</t>
         </is>
       </c>
-      <c r="G82" s="2" t="inlineStr"/>
-      <c r="H82" s="2" t="inlineStr">
+      <c r="G81" s="2" t="inlineStr"/>
+      <c r="H81" s="2" t="inlineStr">
         <is>
           <t>96
  You can now download your quarterly tax report which includes data such as identity information, number of transactions, revenue, and commission and service fees.
@@ -4555,39 +4505,39 @@
         </is>
       </c>
     </row>
-    <row r="83">
-      <c r="A83" s="2" t="inlineStr">
+    <row r="82">
+      <c r="A82" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B83" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C83" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D83" s="2" t="inlineStr">
+      <c r="B82" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C82" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D82" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 15:34:38 +0000</t>
         </is>
       </c>
-      <c r="E83" s="2" t="inlineStr">
+      <c r="E82" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F83" s="2" t="inlineStr">
+      <c r="F82" s="2" t="inlineStr">
         <is>
           <t>Three weeks out. Have you registered?</t>
         </is>
       </c>
-      <c r="G83" s="2" t="inlineStr"/>
-      <c r="H83" s="2" t="inlineStr">
+      <c r="G82" s="2" t="inlineStr"/>
+      <c r="H82" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-31/7z5hj8h/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5hj8l/6865258013/h/R4H_C9NHvcjNXDhguSu8h5kLS8rvmJFLgxujNzlVtzg)
@@ -4601,39 +4551,39 @@
         </is>
       </c>
     </row>
-    <row r="84">
-      <c r="A84" s="2" t="inlineStr">
+    <row r="83">
+      <c r="A83" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B84" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C84" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D84" s="2" t="inlineStr">
+      <c r="B83" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C83" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D83" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:47:19 +0000</t>
         </is>
       </c>
-      <c r="E84" s="2" t="inlineStr">
+      <c r="E83" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F84" s="2" t="inlineStr">
+      <c r="F83" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G84" s="2" t="inlineStr"/>
-      <c r="H84" s="2" t="inlineStr">
+      <c r="G83" s="2" t="inlineStr"/>
+      <c r="H83" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4653,39 +4603,39 @@
         </is>
       </c>
     </row>
-    <row r="85">
-      <c r="A85" s="2" t="inlineStr">
+    <row r="84">
+      <c r="A84" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B85" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C85" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D85" s="2" t="inlineStr">
+      <c r="B84" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C84" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D84" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:54 +0000</t>
         </is>
       </c>
-      <c r="E85" s="2" t="inlineStr">
+      <c r="E84" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F85" s="2" t="inlineStr">
+      <c r="F84" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G85" s="2" t="inlineStr"/>
-      <c r="H85" s="2" t="inlineStr">
+      <c r="G84" s="2" t="inlineStr"/>
+      <c r="H84" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4702,39 +4652,39 @@
         </is>
       </c>
     </row>
-    <row r="86">
-      <c r="A86" s="2" t="inlineStr">
+    <row r="85">
+      <c r="A85" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B86" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C86" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D86" s="2" t="inlineStr">
+      <c r="B85" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C85" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D85" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 13:38:25 +0000</t>
         </is>
       </c>
-      <c r="E86" s="2" t="inlineStr">
+      <c r="E85" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F86" s="2" t="inlineStr">
+      <c r="F85" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G86" s="2" t="inlineStr"/>
-      <c r="H86" s="2" t="inlineStr">
+      <c r="G85" s="2" t="inlineStr"/>
+      <c r="H85" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4754,39 +4704,39 @@
         </is>
       </c>
     </row>
-    <row r="87">
-      <c r="A87" s="2" t="inlineStr">
+    <row r="86">
+      <c r="A86" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B87" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C87" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D87" s="2" t="inlineStr">
+      <c r="B86" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C86" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D86" s="2" t="inlineStr">
         <is>
           <t>Tue, 1 Sep 2026 10:39:58 +0000</t>
         </is>
       </c>
-      <c r="E87" s="2" t="inlineStr">
+      <c r="E86" s="2" t="inlineStr">
         <is>
           <t>Amazon Europe &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F87" s="2" t="inlineStr">
+      <c r="F86" s="2" t="inlineStr">
         <is>
           <t>Envía los números de registro de RAP antes del 30 de junio</t>
         </is>
       </c>
-      <c r="G87" s="2" t="inlineStr"/>
-      <c r="H87" s="2" t="inlineStr">
+      <c r="G86" s="2" t="inlineStr"/>
+      <c r="H86" s="2" t="inlineStr">
         <is>
           <t>96
  You’ll be enrolled in EPR Pay on Behalf unless you provide valid Extended Producer Responsibility registration numbers by June 30
@@ -4795,39 +4745,39 @@
         </is>
       </c>
     </row>
-    <row r="88">
-      <c r="A88" s="2" t="inlineStr">
+    <row r="87">
+      <c r="A87" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B88" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C88" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D88" s="2" t="inlineStr">
+      <c r="B87" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C87" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D87" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 10:29:17 +0000</t>
         </is>
       </c>
-      <c r="E88" s="2" t="inlineStr">
+      <c r="E87" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F88" s="2" t="inlineStr">
+      <c r="F87" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends this Saturday—Register now</t>
         </is>
       </c>
-      <c r="G88" s="2" t="inlineStr"/>
-      <c r="H88" s="2" t="inlineStr">
+      <c r="G87" s="2" t="inlineStr"/>
+      <c r="H87" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-26/7z5f1dw/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5f1dz/6858839240/h/an0hGAbEsn_GcD7m8vCy3PA0zGSpSHw1r6FwW9L-zGQ)
@@ -4846,39 +4796,39 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="2" t="inlineStr">
+    <row r="88">
+      <c r="A88" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B89" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C89" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D89" s="2" t="inlineStr">
+      <c r="B88" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C88" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D88" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:42:21 +0000</t>
         </is>
       </c>
-      <c r="E89" s="2" t="inlineStr">
+      <c r="E88" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F89" s="2" t="inlineStr">
+      <c r="F88" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G89" s="2" t="inlineStr"/>
-      <c r="H89" s="2" t="inlineStr">
+      <c r="G88" s="2" t="inlineStr"/>
+      <c r="H88" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4895,39 +4845,39 @@
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" s="2" t="inlineStr">
+    <row r="89">
+      <c r="A89" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B90" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C90" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D90" s="2" t="inlineStr">
+      <c r="B89" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C89" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D89" s="2" t="inlineStr">
         <is>
           <t>Sat, 29 Aug 2026 00:41:47 +0000</t>
         </is>
       </c>
-      <c r="E90" s="2" t="inlineStr">
+      <c r="E89" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F90" s="2" t="inlineStr">
+      <c r="F89" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G90" s="2" t="inlineStr"/>
-      <c r="H90" s="2" t="inlineStr">
+      <c r="G89" s="2" t="inlineStr"/>
+      <c r="H89" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -4947,39 +4897,39 @@
         </is>
       </c>
     </row>
-    <row r="91">
-      <c r="A91" s="2" t="inlineStr">
+    <row r="90">
+      <c r="A90" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B91" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C91" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D91" s="2" t="inlineStr">
+      <c r="B90" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C90" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D90" s="2" t="inlineStr">
         <is>
           <t>Thu, 27 Aug 2026 10:23:35 +0000</t>
         </is>
       </c>
-      <c r="E91" s="2" t="inlineStr">
+      <c r="E90" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F91" s="2" t="inlineStr">
+      <c r="F90" s="2" t="inlineStr">
         <is>
           <t>Final Call: Early-bird pricing ends this Saturday, 8/29—Register now</t>
         </is>
       </c>
-      <c r="G91" s="2" t="inlineStr"/>
-      <c r="H91" s="2" t="inlineStr">
+      <c r="G90" s="2" t="inlineStr"/>
+      <c r="H90" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-25/7z5dp4h/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dp4l/6853578557/h/fMcSGqjdqgEDoIsJN08zOUUgHxkKkP49uaYlySvIDk8)
@@ -4998,39 +4948,39 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="2" t="inlineStr">
+    <row r="91">
+      <c r="A91" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B92" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C92" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D92" s="2" t="inlineStr">
+      <c r="B91" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C91" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D91" s="2" t="inlineStr">
         <is>
           <t>Wed, 26 Aug 2026 12:33:59 +0000</t>
         </is>
       </c>
-      <c r="E92" s="2" t="inlineStr">
+      <c r="E91" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F92" s="2" t="inlineStr">
+      <c r="F91" s="2" t="inlineStr">
         <is>
           <t>Sellers called this one of the highlights of Accelerate</t>
         </is>
       </c>
-      <c r="G92" s="2" t="inlineStr"/>
-      <c r="H92" s="2" t="inlineStr">
+      <c r="G91" s="2" t="inlineStr"/>
+      <c r="H91" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-24/7z5dhr3/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z5dhr6/6851676170/h/Wjp-bmbnJMm0YNVflBOldr6STH8h5YJsrXHhgAzeKUo)
@@ -5046,39 +4996,39 @@
         </is>
       </c>
     </row>
-    <row r="93">
-      <c r="A93" s="2" t="inlineStr">
+    <row r="92">
+      <c r="A92" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B93" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C93" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D93" s="2" t="inlineStr">
+      <c r="B92" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C92" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D92" s="2" t="inlineStr">
         <is>
           <t>Tue, 25 Aug 2026 12:24:04 +0000</t>
         </is>
       </c>
-      <c r="E93" s="2" t="inlineStr">
+      <c r="E92" s="2" t="inlineStr">
         <is>
           <t>"donotreply@amazon.com" &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F93" s="2" t="inlineStr">
+      <c r="F92" s="2" t="inlineStr">
         <is>
           <t>✅ Transparency Payment Confirmed!</t>
         </is>
       </c>
-      <c r="G93" s="2" t="inlineStr"/>
-      <c r="H93" s="2" t="inlineStr">
+      <c r="G92" s="2" t="inlineStr"/>
+      <c r="H92" s="2" t="inlineStr">
         <is>
           <t>96
  Hello,
@@ -5102,39 +5052,39 @@
         </is>
       </c>
     </row>
-    <row r="94">
-      <c r="A94" s="2" t="inlineStr">
+    <row r="93">
+      <c r="A93" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B94" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C94" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D94" s="2" t="inlineStr">
+      <c r="B93" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C93" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D93" s="2" t="inlineStr">
         <is>
           <t>Mon, 24 Aug 2026 12:38:26 +0000</t>
         </is>
       </c>
-      <c r="E94" s="2" t="inlineStr">
+      <c r="E93" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F94" s="2" t="inlineStr">
+      <c r="F93" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends August 29. Save $100 now</t>
         </is>
       </c>
-      <c r="G94" s="2" t="inlineStr"/>
-      <c r="H94" s="2" t="inlineStr">
+      <c r="G93" s="2" t="inlineStr"/>
+      <c r="H93" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596lw/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596lz/6847886297/h/fajszjfN78xb3oKGP7qMLJQXUM-VqKc8irnBicIIs-Y)
@@ -5150,39 +5100,39 @@
         </is>
       </c>
     </row>
-    <row r="95">
-      <c r="A95" s="2" t="inlineStr">
+    <row r="94">
+      <c r="A94" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B95" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C95" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D95" s="2" t="inlineStr">
+      <c r="B94" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C94" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D94" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:31 +0000</t>
         </is>
       </c>
-      <c r="E95" s="2" t="inlineStr">
+      <c r="E94" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F95" s="2" t="inlineStr">
+      <c r="F94" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G95" s="2" t="inlineStr"/>
-      <c r="H95" s="2" t="inlineStr">
+      <c r="G94" s="2" t="inlineStr"/>
+      <c r="H94" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5199,39 +5149,39 @@
         </is>
       </c>
     </row>
-    <row r="96">
-      <c r="A96" s="2" t="inlineStr">
+    <row r="95">
+      <c r="A95" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B96" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C96" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D96" s="2" t="inlineStr">
+      <c r="B95" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C95" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D95" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 17:14:20 +0000</t>
         </is>
       </c>
-      <c r="E96" s="2" t="inlineStr">
+      <c r="E95" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F96" s="2" t="inlineStr">
+      <c r="F95" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G96" s="2" t="inlineStr"/>
-      <c r="H96" s="2" t="inlineStr">
+      <c r="G95" s="2" t="inlineStr"/>
+      <c r="H95" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5251,39 +5201,39 @@
         </is>
       </c>
     </row>
-    <row r="97">
-      <c r="A97" s="2" t="inlineStr">
+    <row r="96">
+      <c r="A96" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B97" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C97" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D97" s="2" t="inlineStr">
+      <c r="B96" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C96" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D96" s="2" t="inlineStr">
         <is>
           <t>Sat, 22 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E97" s="2" t="inlineStr">
+      <c r="E96" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F97" s="2" t="inlineStr">
+      <c r="F96" s="2" t="inlineStr">
         <is>
           <t>Early-bird pricing ends Saturday, Aug. 29—Save $100 before it's full price</t>
         </is>
       </c>
-      <c r="G97" s="2" t="inlineStr"/>
-      <c r="H97" s="2" t="inlineStr">
+      <c r="G96" s="2" t="inlineStr"/>
+      <c r="H96" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-19/7z596mz/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
 [Early-bird ending soon](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z596n3/6845766770/h/4MOe7WIB0iKog9ZJ2gooAw5JI3-zJ2xmrM13S4lZjTw)
@@ -5299,40 +5249,40 @@
         </is>
       </c>
     </row>
-    <row r="98">
-      <c r="A98" s="2" t="inlineStr">
+    <row r="97">
+      <c r="A97" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B98" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C98" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D98" s="2" t="inlineStr">
+      <c r="B97" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C97" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D97" s="2" t="inlineStr">
         <is>
           <t>Fri, 21 Aug 2026 10:16:19 +0000</t>
         </is>
       </c>
-      <c r="E98" s="2" t="inlineStr">
+      <c r="E97" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F98" s="2" t="inlineStr">
+      <c r="F97" s="2" t="inlineStr">
         <is>
           <t>The fireside chat we teased is here. Early-bird pricing ends next
  week.</t>
         </is>
       </c>
-      <c r="G98" s="2" t="inlineStr"/>
-      <c r="H98" s="2" t="inlineStr">
+      <c r="G97" s="2" t="inlineStr"/>
+      <c r="H97" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bwt/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58bwx/6843878552/h/i5ZL7d6_GwNwKOo6-EVWTgdYbnnn0rhnWQ2kP-UgsCs)
@@ -5348,39 +5298,39 @@
         </is>
       </c>
     </row>
-    <row r="99">
-      <c r="A99" s="2" t="inlineStr">
+    <row r="98">
+      <c r="A98" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B99" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C99" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D99" s="2" t="inlineStr">
+      <c r="B98" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C98" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D98" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:05:40 +0000</t>
         </is>
       </c>
-      <c r="E99" s="2" t="inlineStr">
+      <c r="E98" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F99" s="2" t="inlineStr">
+      <c r="F98" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G99" s="2" t="inlineStr"/>
-      <c r="H99" s="2" t="inlineStr">
+      <c r="G98" s="2" t="inlineStr"/>
+      <c r="H98" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5400,39 +5350,39 @@
         </is>
       </c>
     </row>
-    <row r="100">
-      <c r="A100" s="2" t="inlineStr">
+    <row r="99">
+      <c r="A99" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B100" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C100" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D100" s="2" t="inlineStr">
+      <c r="B99" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C99" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D99" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:47 +0000</t>
         </is>
       </c>
-      <c r="E100" s="2" t="inlineStr">
+      <c r="E99" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F100" s="2" t="inlineStr">
+      <c r="F99" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G100" s="2" t="inlineStr"/>
-      <c r="H100" s="2" t="inlineStr">
+      <c r="G99" s="2" t="inlineStr"/>
+      <c r="H99" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">96
 This title will display on mobile devices
@@ -5449,39 +5399,39 @@
         </is>
       </c>
     </row>
-    <row r="101">
-      <c r="A101" s="2" t="inlineStr">
+    <row r="100">
+      <c r="A100" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B101" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C101" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D101" s="2" t="inlineStr">
+      <c r="B100" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C100" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D100" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 16:03:34 +0000</t>
         </is>
       </c>
-      <c r="E101" s="2" t="inlineStr">
+      <c r="E100" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F101" s="2" t="inlineStr">
+      <c r="F100" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G101" s="2" t="inlineStr"/>
-      <c r="H101" s="2" t="inlineStr">
+      <c r="G100" s="2" t="inlineStr"/>
+      <c r="H100" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5501,39 +5451,39 @@
         </is>
       </c>
     </row>
-    <row r="102">
-      <c r="A102" s="2" t="inlineStr">
+    <row r="101">
+      <c r="A101" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B102" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C102" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D102" s="2" t="inlineStr">
+      <c r="B101" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C101" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D101" s="2" t="inlineStr">
         <is>
           <t>Thu, 20 Aug 2026 12:23:03 +0000</t>
         </is>
       </c>
-      <c r="E102" s="2" t="inlineStr">
+      <c r="E101" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F102" s="2" t="inlineStr">
+      <c r="F101" s="2" t="inlineStr">
         <is>
           <t>You're exactly who Accelerate was designed for</t>
         </is>
       </c>
-      <c r="G102" s="2" t="inlineStr"/>
-      <c r="H102" s="2" t="inlineStr">
+      <c r="G101" s="2" t="inlineStr"/>
+      <c r="H101" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-18/7z58zcm/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
 [Your next level starts here](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58zcq/6842423531/h/zqV8R_k6k7yKhqDq4dX1yXmefn5JIN40lXum5Y6M4KM)
@@ -5548,40 +5498,40 @@
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="2" t="inlineStr">
+    <row r="102">
+      <c r="A102" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B103" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C103" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D103" s="2" t="inlineStr">
+      <c r="B102" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C102" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D102" s="2" t="inlineStr">
         <is>
           <t>Tue, 18 Aug 2026 12:13:14 +0000</t>
         </is>
       </c>
-      <c r="E103" s="2" t="inlineStr">
+      <c r="E102" s="2" t="inlineStr">
         <is>
           <t>Amazon Accelerate &lt;no-reply@sell.amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F103" s="2" t="inlineStr">
+      <c r="F102" s="2" t="inlineStr">
         <is>
           <t>Live at Accelerate 2026: Mary Beth Westmoreland and Amit Agarwal
  fireside chat</t>
         </is>
       </c>
-      <c r="G103" s="2" t="inlineStr"/>
-      <c r="H103" s="2" t="inlineStr">
+      <c r="G102" s="2" t="inlineStr"/>
+      <c r="H102" s="2" t="inlineStr">
         <is>
           <t>[Amazon logo](https://go.amazonsellerservices.com/e/229492/2026-08-17/7z58bxx/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
 [Partner Connect at Accelerate 2026](https://go.amazonsellerservices.com/e/229492/-medium-email-utm-source-email/7z58by1/6837257199/h/ROTGYDonH0Pvpb92J9CZAGdoz2-iazjSlqoOkDG1azg)
@@ -5594,39 +5544,39 @@
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="2" t="inlineStr">
+    <row r="103">
+      <c r="A103" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B104" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C104" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D104" s="2" t="inlineStr">
+      <c r="B103" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C103" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D103" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:27:13 +0000</t>
         </is>
       </c>
-      <c r="E104" s="2" t="inlineStr">
+      <c r="E103" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F104" s="2" t="inlineStr">
+      <c r="F103" s="2" t="inlineStr">
         <is>
           <t>Tu pago está en camino</t>
         </is>
       </c>
-      <c r="G104" s="2" t="inlineStr"/>
-      <c r="H104" s="2" t="inlineStr">
+      <c r="G103" s="2" t="inlineStr"/>
+      <c r="H103" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5643,39 +5593,39 @@
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="2" t="inlineStr">
+    <row r="104">
+      <c r="A104" s="2" t="inlineStr">
         <is>
           <t>付款/资金类</t>
         </is>
       </c>
-      <c r="B105" s="2" t="inlineStr">
-        <is>
-          <t>older</t>
-        </is>
-      </c>
-      <c r="C105" s="2" t="inlineStr">
-        <is>
-          <t>account_4</t>
-        </is>
-      </c>
-      <c r="D105" s="2" t="inlineStr">
+      <c r="B104" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C104" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D104" s="2" t="inlineStr">
         <is>
           <t>Mon, 17 Aug 2026 18:26:45 +0000</t>
         </is>
       </c>
-      <c r="E105" s="2" t="inlineStr">
+      <c r="E104" s="2" t="inlineStr">
         <is>
           <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
         </is>
       </c>
-      <c r="F105" s="2" t="inlineStr">
+      <c r="F104" s="2" t="inlineStr">
         <is>
           <t>Your payment is on the way</t>
         </is>
       </c>
-      <c r="G105" s="2" t="inlineStr"/>
-      <c r="H105" s="2" t="inlineStr">
+      <c r="G104" s="2" t="inlineStr"/>
+      <c r="H104" s="2" t="inlineStr">
         <is>
           <t>96
 This title will display on mobile devices
@@ -5692,6 +5642,56 @@
 Thank you for selling in the Amazon store,
 Amazon Services
 Help us improve your payment experience on Ama</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="2" t="inlineStr">
+        <is>
+          <t>产品链接/合规类</t>
+        </is>
+      </c>
+      <c r="B105" s="2" t="inlineStr">
+        <is>
+          <t>older</t>
+        </is>
+      </c>
+      <c r="C105" s="2" t="inlineStr">
+        <is>
+          <t>account_4</t>
+        </is>
+      </c>
+      <c r="D105" s="2" t="inlineStr">
+        <is>
+          <t>Wed, 9 Sep 2026 18:07:39 +0000</t>
+        </is>
+      </c>
+      <c r="E105" s="2" t="inlineStr">
+        <is>
+          <t>Amazon Services &lt;donotreply@amazon.com&gt;</t>
+        </is>
+      </c>
+      <c r="F105" s="2" t="inlineStr">
+        <is>
+          <t>Submit product safety documentation to reactivate listings</t>
+        </is>
+      </c>
+      <c r="G105" s="2" t="inlineStr"/>
+      <c r="H105" s="2" t="inlineStr">
+        <is>
+          <t xml:space="preserve">96
+ Submit product safety documentation to reactivate listings
+ Hello Weihai CA,
+ Some of your listings have been deactivated due to missing mandatory compliance requirements for your products. Review the details and next steps below. The affected listings are shown at the end of this email.
+ Why is this happening?
+ We are taking this action because these products are missing mandatory compliance information. Review our Product safety and compliance help page for information on applicable laws, regulations and Amazon policies. We leveraged a combination of automated means and expert human review to identify this issue and make this decision.
+ The table at the end of this email provides product-specific compliance requirements.
+ How do I reactivate my listings?
+ To provide the required compliance information, go to your Account Health page and locate the product compliance requests:
+-
+ If you have the required documentation, follow the instructions to submit your compliance documents. We will only reinstate products that fulfil the compliance requirements.
+-
+ If you believe your products are exempt from these requirements, submit documentation demonstrating why they are not subject </t>
         </is>
       </c>
     </row>
